--- a/우리금융지주_연결_결과.xlsx
+++ b/우리금융지주_연결_결과.xlsx
@@ -11,7 +11,8 @@
     <sheet name="재무제표" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="재무비율" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="상세보기_원항목추이" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="검증" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="스크리닝_전기당기증감" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="검증" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -87,7 +88,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -98,16 +99,24 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="00FFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FF4C4C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1126,7 +1135,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>연결재무제표(CFS) — 링크가 가리키는 문서('(첨부)연결재무제표') 기준으로 자동 선택됨</t>
+          <t>연결재무제표(CFS)</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4375,919 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:G39"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="186" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>전기 대비 당기 증감 스크리닝 (분석적 절차)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>[안내] 재무상태표/손익계산서/현금흐름표의 개별 계정 중 전기 대비 증감률이 ±10%를 초과하는 계정만 추립니다(중요성 기준 미만 소액 계정은 제외). 신규계정(전기=0)·부호전환(흑자↔적자)은 %를 계산하지 않고 별도 표시합니다. 증감액(절대금액) 내림차순 정렬이며, ±30% 초과는 진하게, ±10~30%는 연하게 강조됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>[경고] 동일 계정명으로 매칭된 금액이 서로 달라 스크리닝에서 제외된 항목</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>[포괄손익계산서] 보험서비스비용: 동일 계정명으로 매칭된 금액이 서로 달라 스크리닝에서 제외됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>[포괄손익계산서] 보험수익: 동일 계정명으로 매칭된 금액이 서로 달라 스크리닝에서 제외됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>[포괄손익계산서] 비지배지분: 동일 계정명으로 매칭된 금액이 서로 달라 스크리닝에서 제외됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>[포괄손익계산서] 지배기업소유주지분: 동일 계정명으로 매칭된 금액이 서로 달라 스크리닝에서 제외됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>[포괄손익계산서] 지분법자본변동: 동일 계정명으로 매칭된 금액이 서로 달라 스크리닝에서 제외됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>[현금흐름표] 위험회피활동으로 인한 현금순증감: 동일 계정명으로 매칭된 금액이 서로 달라 스크리닝에서 제외됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>재무제표구분</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>계정명</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>전기금액</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>당기금액</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>증감액</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>증감률(%)</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>재무상태표</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>부채와자본총계</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="n">
+        <v>525753320000000</v>
+      </c>
+      <c r="D13" s="8" t="n">
+        <v>601457286000000</v>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>75703966000000</v>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>재무상태표</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>자산총계</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="n">
+        <v>525753320000000</v>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>601457286000000</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>75703966000000</v>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>재무상태표</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>부채총계</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="n">
+        <v>489858051000000</v>
+      </c>
+      <c r="D15" s="8" t="n">
+        <v>563598038000000</v>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>73739987000000</v>
+      </c>
+      <c r="F15" s="7" t="n">
+        <v>15.05</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>재무상태표</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>보험계약부채</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="8" t="n">
+        <v>45573864000000</v>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>45573864000000</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>신규계정</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>재무상태표</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>기타포괄손익-공정가치측정금융자산</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="n">
+        <v>43797745000000</v>
+      </c>
+      <c r="D17" s="8" t="n">
+        <v>83499522000000</v>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>39701777000000</v>
+      </c>
+      <c r="F17" s="7" t="n">
+        <v>90.65000000000001</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>현금흐름표</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>영업활동으로 인한 자산ㆍ부채의 변동</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="n">
+        <v>-13479204000000</v>
+      </c>
+      <c r="D18" s="8" t="n">
+        <v>9225268000000</v>
+      </c>
+      <c r="E18" s="8" t="n">
+        <v>22704472000000</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>부호전환</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>현금흐름표</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>영업활동으로 인한 현금흐름</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="n">
+        <v>-6129300000000</v>
+      </c>
+      <c r="D19" s="8" t="n">
+        <v>13642391000000</v>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>19771691000000</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>부호전환</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>현금흐름표</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>현금및현금성자산의 증가(감소)</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="n">
+        <v>-3275495000000</v>
+      </c>
+      <c r="D20" s="8" t="n">
+        <v>11218556000000</v>
+      </c>
+      <c r="E20" s="8" t="n">
+        <v>14494051000000</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>부호전환</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>현금흐름표</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>상각후원가측정대출채권및기타금융자산</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="n">
+        <v>-21703969000000</v>
+      </c>
+      <c r="D21" s="8" t="n">
+        <v>-8369230000000</v>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>13334739000000</v>
+      </c>
+      <c r="F21" s="7" t="n">
+        <v>61.44</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>현금흐름표</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>기타포괄손익-공정가치측정금융자산의 취득</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="n">
+        <v>31718677000000</v>
+      </c>
+      <c r="D22" s="8" t="n">
+        <v>43073556000000</v>
+      </c>
+      <c r="E22" s="8" t="n">
+        <v>11354879000000</v>
+      </c>
+      <c r="F22" s="7" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>재무상태표</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>현금및현금성자산</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="n">
+        <v>27281123000000</v>
+      </c>
+      <c r="D23" s="8" t="n">
+        <v>38499679000000</v>
+      </c>
+      <c r="E23" s="8" t="n">
+        <v>11218556000000</v>
+      </c>
+      <c r="F23" s="7" t="n">
+        <v>41.12</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>현금흐름표</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>현금및현금성자산</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="n">
+        <v>27281123000000</v>
+      </c>
+      <c r="D24" s="8" t="n">
+        <v>38499679000000</v>
+      </c>
+      <c r="E24" s="8" t="n">
+        <v>11218556000000</v>
+      </c>
+      <c r="F24" s="7" t="n">
+        <v>41.12</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>현금흐름표</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>예수부채</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="n">
+        <v>3411535000000</v>
+      </c>
+      <c r="D25" s="8" t="n">
+        <v>13839807000000</v>
+      </c>
+      <c r="E25" s="8" t="n">
+        <v>10428272000000</v>
+      </c>
+      <c r="F25" s="7" t="n">
+        <v>305.68</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>현금흐름표</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>투자활동으로 인한 현금흐름</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="n">
+        <v>-34299000000</v>
+      </c>
+      <c r="D26" s="8" t="n">
+        <v>-9880603000000</v>
+      </c>
+      <c r="E26" s="8" t="n">
+        <v>-9846304000000</v>
+      </c>
+      <c r="F26" s="7" t="n">
+        <v>-28707.26</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>재무상태표</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>당기손익-공정가치측정금융자산</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="n">
+        <v>25202672000000</v>
+      </c>
+      <c r="D27" s="8" t="n">
+        <v>34245475000000</v>
+      </c>
+      <c r="E27" s="8" t="n">
+        <v>9042803000000</v>
+      </c>
+      <c r="F27" s="7" t="n">
+        <v>35.88</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>현금흐름표</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>당기손익-공정가치측정금융상품의 취득</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="n">
+        <v>11111809000000</v>
+      </c>
+      <c r="D28" s="8" t="n">
+        <v>20087654000000</v>
+      </c>
+      <c r="E28" s="8" t="n">
+        <v>8975845000000</v>
+      </c>
+      <c r="F28" s="7" t="n">
+        <v>80.78</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>현금흐름표</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>기타포괄손익-공정가치측정금융자산의 처분</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="n">
+        <v>26921313000000</v>
+      </c>
+      <c r="D29" s="8" t="n">
+        <v>35153473000000</v>
+      </c>
+      <c r="E29" s="8" t="n">
+        <v>8232160000000</v>
+      </c>
+      <c r="F29" s="7" t="n">
+        <v>30.58</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>현금흐름표</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>당기손익-공정가치측정금융상품의 처분</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="n">
+        <v>11659750000000</v>
+      </c>
+      <c r="D30" s="8" t="n">
+        <v>19103867000000</v>
+      </c>
+      <c r="E30" s="8" t="n">
+        <v>7444117000000</v>
+      </c>
+      <c r="F30" s="7" t="n">
+        <v>63.84</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>재무상태표</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>발행사채</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="n">
+        <v>48207103000000</v>
+      </c>
+      <c r="D31" s="8" t="n">
+        <v>55583392000000</v>
+      </c>
+      <c r="E31" s="8" t="n">
+        <v>7376289000000</v>
+      </c>
+      <c r="F31" s="7" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>현금흐름표</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>재무활동으로 인한 현금흐름</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="n">
+        <v>1245341000000</v>
+      </c>
+      <c r="D32" s="8" t="n">
+        <v>7685336000000</v>
+      </c>
+      <c r="E32" s="8" t="n">
+        <v>6439995000000</v>
+      </c>
+      <c r="F32" s="7" t="n">
+        <v>517.13</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>재무상태표</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>기타금융부채</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="n">
+        <v>32314051000000</v>
+      </c>
+      <c r="D33" s="8" t="n">
+        <v>38118058000000</v>
+      </c>
+      <c r="E33" s="8" t="n">
+        <v>5804007000000</v>
+      </c>
+      <c r="F33" s="7" t="n">
+        <v>17.96</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>재무상태표</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>차입부채</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="n">
+        <v>30117031000000</v>
+      </c>
+      <c r="D34" s="8" t="n">
+        <v>34183267000000</v>
+      </c>
+      <c r="E34" s="8" t="n">
+        <v>4066236000000</v>
+      </c>
+      <c r="F34" s="7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>현금흐름표</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>발행사채의 상환</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="n">
+        <v>35473345000000</v>
+      </c>
+      <c r="D35" s="8" t="n">
+        <v>31611225000000</v>
+      </c>
+      <c r="E35" s="8" t="n">
+        <v>-3862120000000</v>
+      </c>
+      <c r="F35" s="7" t="n">
+        <v>-10.89</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>재무상태표</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>당기손익-공정가치측정금융부채</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="n">
+        <v>9896597000000</v>
+      </c>
+      <c r="D36" s="8" t="n">
+        <v>6356934000000</v>
+      </c>
+      <c r="E36" s="8" t="n">
+        <v>-3539663000000</v>
+      </c>
+      <c r="F36" s="7" t="n">
+        <v>-35.77</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>현금흐름표</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>기초 현금및현금성자산</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="n">
+        <v>30556618000000</v>
+      </c>
+      <c r="D37" s="8" t="n">
+        <v>27281123000000</v>
+      </c>
+      <c r="E37" s="8" t="n">
+        <v>-3275495000000</v>
+      </c>
+      <c r="F37" s="7" t="n">
+        <v>-10.72</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>현금흐름표</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>상각후원가측정유가증권의 상환</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="n">
+        <v>7634677000000</v>
+      </c>
+      <c r="D38" s="8" t="n">
+        <v>5900990000000</v>
+      </c>
+      <c r="E38" s="8" t="n">
+        <v>-1733687000000</v>
+      </c>
+      <c r="F38" s="7" t="n">
+        <v>-22.71</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>포괄손익계산서</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>상각후원가측정금융부채 이자비용</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="n">
+        <v>13127005000000</v>
+      </c>
+      <c r="D39" s="8" t="n">
+        <v>11401953000000</v>
+      </c>
+      <c r="E39" s="8" t="n">
+        <v>-1725052000000</v>
+      </c>
+      <c r="F39" s="7" t="n">
+        <v>-13.14</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>정상</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F13:F39">
+    <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="1">
+      <formula>30.0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="1">
+      <formula>-30.0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="between" dxfId="0">
+      <formula>10.0</formula>
+      <formula>30.0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="between" dxfId="0">
+      <formula>-30.0</formula>
+      <formula>-10.0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="125" customWidth="1" min="1" max="1"/>
@@ -4392,9 +5313,9 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>✓ 전체 9건 모두 일치 (검증 통과)</t>
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>✓ 전체 92건 모두 일치 (검증 통과)</t>
         </is>
       </c>
     </row>
@@ -4676,6 +5597,1951 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>3) 전기 대비 당기 증감 스크리닝 검증 (원본금액 대사 + 증감률/분류 재계산 + 전수 검사)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>검증항목</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>기간</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>기준값</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>재계산값</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>일치여부</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 재무상태표 부채와자본총계 (전기)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="n">
+        <v>525753320000000</v>
+      </c>
+      <c r="D25" s="7" t="n">
+        <v>525753320000000</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 재무상태표 부채와자본총계 (당기)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="n">
+        <v>601457286000000</v>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>601457286000000</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 재무상태표 부채와자본총계</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 재무상태표 자산총계 (전기)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="n">
+        <v>525753320000000</v>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>525753320000000</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 재무상태표 자산총계 (당기)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="n">
+        <v>601457286000000</v>
+      </c>
+      <c r="D29" s="7" t="n">
+        <v>601457286000000</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 재무상태표 자산총계</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="D30" s="7" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 재무상태표 부채총계 (전기)</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="n">
+        <v>489858051000000</v>
+      </c>
+      <c r="D31" s="7" t="n">
+        <v>489858051000000</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 재무상태표 부채총계 (당기)</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="n">
+        <v>563598038000000</v>
+      </c>
+      <c r="D32" s="7" t="n">
+        <v>563598038000000</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 재무상태표 부채총계</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="n">
+        <v>15.05</v>
+      </c>
+      <c r="D33" s="7" t="n">
+        <v>15.05</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 재무상태표 보험계약부채 (전기)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 재무상태표 보험계약부채 (당기)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="n">
+        <v>45573864000000</v>
+      </c>
+      <c r="D35" s="7" t="n">
+        <v>45573864000000</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>[스크리닝-분류:신규계정] 재무상태표 보험계약부채</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 재무상태표 기타포괄손익-공정가치측정금융자산 (전기)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="n">
+        <v>43797745000000</v>
+      </c>
+      <c r="D37" s="7" t="n">
+        <v>43797745000000</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 재무상태표 기타포괄손익-공정가치측정금융자산 (당기)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="n">
+        <v>83499522000000</v>
+      </c>
+      <c r="D38" s="7" t="n">
+        <v>83499522000000</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 재무상태표 기타포괄손익-공정가치측정금융자산</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="n">
+        <v>90.65000000000001</v>
+      </c>
+      <c r="D39" s="7" t="n">
+        <v>90.65000000000001</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 영업활동으로 인한 자산ㆍ부채의 변동 (전기)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="n">
+        <v>-13479204000000</v>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>-13479204000000</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 영업활동으로 인한 자산ㆍ부채의 변동 (당기)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="n">
+        <v>9225268000000</v>
+      </c>
+      <c r="D41" s="7" t="n">
+        <v>9225268000000</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>[스크리닝-분류:부호전환] 현금흐름표 영업활동으로 인한 자산ㆍ부채의 변동</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 영업활동으로 인한 현금흐름 (전기)</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="n">
+        <v>-6129300000000</v>
+      </c>
+      <c r="D43" s="7" t="n">
+        <v>-6129300000000</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 영업활동으로 인한 현금흐름 (당기)</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="n">
+        <v>13642391000000</v>
+      </c>
+      <c r="D44" s="7" t="n">
+        <v>13642391000000</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>[스크리닝-분류:부호전환] 현금흐름표 영업활동으로 인한 현금흐름</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 현금및현금성자산의 증가(감소) (전기)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="n">
+        <v>-3275495000000</v>
+      </c>
+      <c r="D46" s="7" t="n">
+        <v>-3275495000000</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 현금및현금성자산의 증가(감소) (당기)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="n">
+        <v>11218556000000</v>
+      </c>
+      <c r="D47" s="7" t="n">
+        <v>11218556000000</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>[스크리닝-분류:부호전환] 현금흐름표 현금및현금성자산의 증가(감소)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 상각후원가측정대출채권및기타금융자산 (전기)</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="n">
+        <v>-21703969000000</v>
+      </c>
+      <c r="D49" s="7" t="n">
+        <v>-21703969000000</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 상각후원가측정대출채권및기타금융자산 (당기)</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="n">
+        <v>-8369230000000</v>
+      </c>
+      <c r="D50" s="7" t="n">
+        <v>-8369230000000</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 현금흐름표 상각후원가측정대출채권및기타금융자산</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="n">
+        <v>61.44</v>
+      </c>
+      <c r="D51" s="7" t="n">
+        <v>61.44</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 기타포괄손익-공정가치측정금융자산의 취득 (전기)</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="n">
+        <v>31718677000000</v>
+      </c>
+      <c r="D52" s="7" t="n">
+        <v>31718677000000</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 기타포괄손익-공정가치측정금융자산의 취득 (당기)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="n">
+        <v>43073556000000</v>
+      </c>
+      <c r="D53" s="7" t="n">
+        <v>43073556000000</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 현금흐름표 기타포괄손익-공정가치측정금융자산의 취득</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="D54" s="7" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 재무상태표 현금및현금성자산 (전기)</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="n">
+        <v>27281123000000</v>
+      </c>
+      <c r="D55" s="7" t="n">
+        <v>27281123000000</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 재무상태표 현금및현금성자산 (당기)</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="n">
+        <v>38499679000000</v>
+      </c>
+      <c r="D56" s="7" t="n">
+        <v>38499679000000</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 재무상태표 현금및현금성자산</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="n">
+        <v>41.12</v>
+      </c>
+      <c r="D57" s="7" t="n">
+        <v>41.12</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 현금및현금성자산 (전기)</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C58" s="7" t="n">
+        <v>27281123000000</v>
+      </c>
+      <c r="D58" s="7" t="n">
+        <v>27281123000000</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 현금및현금성자산 (당기)</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="n">
+        <v>38499679000000</v>
+      </c>
+      <c r="D59" s="7" t="n">
+        <v>38499679000000</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 현금흐름표 현금및현금성자산</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C60" s="7" t="n">
+        <v>41.12</v>
+      </c>
+      <c r="D60" s="7" t="n">
+        <v>41.12</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 예수부채 (전기)</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="n">
+        <v>3411535000000</v>
+      </c>
+      <c r="D61" s="7" t="n">
+        <v>3411535000000</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 예수부채 (당기)</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="n">
+        <v>13839807000000</v>
+      </c>
+      <c r="D62" s="7" t="n">
+        <v>13839807000000</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 현금흐름표 예수부채</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C63" s="7" t="n">
+        <v>305.68</v>
+      </c>
+      <c r="D63" s="7" t="n">
+        <v>305.68</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 투자활동으로 인한 현금흐름 (전기)</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="n">
+        <v>-34299000000</v>
+      </c>
+      <c r="D64" s="7" t="n">
+        <v>-34299000000</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 투자활동으로 인한 현금흐름 (당기)</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C65" s="7" t="n">
+        <v>-9880603000000</v>
+      </c>
+      <c r="D65" s="7" t="n">
+        <v>-9880603000000</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 현금흐름표 투자활동으로 인한 현금흐름</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C66" s="7" t="n">
+        <v>-28707.26</v>
+      </c>
+      <c r="D66" s="7" t="n">
+        <v>-28707.26</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 재무상태표 당기손익-공정가치측정금융자산 (전기)</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="n">
+        <v>25202672000000</v>
+      </c>
+      <c r="D67" s="7" t="n">
+        <v>25202672000000</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 재무상태표 당기손익-공정가치측정금융자산 (당기)</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C68" s="7" t="n">
+        <v>34245475000000</v>
+      </c>
+      <c r="D68" s="7" t="n">
+        <v>34245475000000</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 재무상태표 당기손익-공정가치측정금융자산</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C69" s="7" t="n">
+        <v>35.88</v>
+      </c>
+      <c r="D69" s="7" t="n">
+        <v>35.88</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 당기손익-공정가치측정금융상품의 취득 (전기)</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="n">
+        <v>11111809000000</v>
+      </c>
+      <c r="D70" s="7" t="n">
+        <v>11111809000000</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 당기손익-공정가치측정금융상품의 취득 (당기)</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C71" s="7" t="n">
+        <v>20087654000000</v>
+      </c>
+      <c r="D71" s="7" t="n">
+        <v>20087654000000</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 현금흐름표 당기손익-공정가치측정금융상품의 취득</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C72" s="7" t="n">
+        <v>80.78</v>
+      </c>
+      <c r="D72" s="7" t="n">
+        <v>80.78</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 기타포괄손익-공정가치측정금융자산의 처분 (전기)</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C73" s="7" t="n">
+        <v>26921313000000</v>
+      </c>
+      <c r="D73" s="7" t="n">
+        <v>26921313000000</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 기타포괄손익-공정가치측정금융자산의 처분 (당기)</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C74" s="7" t="n">
+        <v>35153473000000</v>
+      </c>
+      <c r="D74" s="7" t="n">
+        <v>35153473000000</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 현금흐름표 기타포괄손익-공정가치측정금융자산의 처분</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C75" s="7" t="n">
+        <v>30.58</v>
+      </c>
+      <c r="D75" s="7" t="n">
+        <v>30.58</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 당기손익-공정가치측정금융상품의 처분 (전기)</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C76" s="7" t="n">
+        <v>11659750000000</v>
+      </c>
+      <c r="D76" s="7" t="n">
+        <v>11659750000000</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 당기손익-공정가치측정금융상품의 처분 (당기)</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C77" s="7" t="n">
+        <v>19103867000000</v>
+      </c>
+      <c r="D77" s="7" t="n">
+        <v>19103867000000</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 현금흐름표 당기손익-공정가치측정금융상품의 처분</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C78" s="7" t="n">
+        <v>63.84</v>
+      </c>
+      <c r="D78" s="7" t="n">
+        <v>63.84</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 재무상태표 발행사채 (전기)</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C79" s="7" t="n">
+        <v>48207103000000</v>
+      </c>
+      <c r="D79" s="7" t="n">
+        <v>48207103000000</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 재무상태표 발행사채 (당기)</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C80" s="7" t="n">
+        <v>55583392000000</v>
+      </c>
+      <c r="D80" s="7" t="n">
+        <v>55583392000000</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 재무상태표 발행사채</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C81" s="7" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="D81" s="7" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 재무활동으로 인한 현금흐름 (전기)</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C82" s="7" t="n">
+        <v>1245341000000</v>
+      </c>
+      <c r="D82" s="7" t="n">
+        <v>1245341000000</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 재무활동으로 인한 현금흐름 (당기)</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C83" s="7" t="n">
+        <v>7685336000000</v>
+      </c>
+      <c r="D83" s="7" t="n">
+        <v>7685336000000</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 현금흐름표 재무활동으로 인한 현금흐름</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C84" s="7" t="n">
+        <v>517.13</v>
+      </c>
+      <c r="D84" s="7" t="n">
+        <v>517.13</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 재무상태표 기타금융부채 (전기)</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C85" s="7" t="n">
+        <v>32314051000000</v>
+      </c>
+      <c r="D85" s="7" t="n">
+        <v>32314051000000</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 재무상태표 기타금융부채 (당기)</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C86" s="7" t="n">
+        <v>38118058000000</v>
+      </c>
+      <c r="D86" s="7" t="n">
+        <v>38118058000000</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 재무상태표 기타금융부채</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C87" s="7" t="n">
+        <v>17.96</v>
+      </c>
+      <c r="D87" s="7" t="n">
+        <v>17.96</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 재무상태표 차입부채 (전기)</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C88" s="7" t="n">
+        <v>30117031000000</v>
+      </c>
+      <c r="D88" s="7" t="n">
+        <v>30117031000000</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 재무상태표 차입부채 (당기)</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C89" s="7" t="n">
+        <v>34183267000000</v>
+      </c>
+      <c r="D89" s="7" t="n">
+        <v>34183267000000</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 재무상태표 차입부채</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C90" s="7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="D90" s="7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 발행사채의 상환 (전기)</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C91" s="7" t="n">
+        <v>35473345000000</v>
+      </c>
+      <c r="D91" s="7" t="n">
+        <v>35473345000000</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 발행사채의 상환 (당기)</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C92" s="7" t="n">
+        <v>31611225000000</v>
+      </c>
+      <c r="D92" s="7" t="n">
+        <v>31611225000000</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 현금흐름표 발행사채의 상환</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C93" s="7" t="n">
+        <v>-10.89</v>
+      </c>
+      <c r="D93" s="7" t="n">
+        <v>-10.89</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 재무상태표 당기손익-공정가치측정금융부채 (전기)</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C94" s="7" t="n">
+        <v>9896597000000</v>
+      </c>
+      <c r="D94" s="7" t="n">
+        <v>9896597000000</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 재무상태표 당기손익-공정가치측정금융부채 (당기)</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C95" s="7" t="n">
+        <v>6356934000000</v>
+      </c>
+      <c r="D95" s="7" t="n">
+        <v>6356934000000</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 재무상태표 당기손익-공정가치측정금융부채</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C96" s="7" t="n">
+        <v>-35.77</v>
+      </c>
+      <c r="D96" s="7" t="n">
+        <v>-35.77</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 기초 현금및현금성자산 (전기)</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C97" s="7" t="n">
+        <v>30556618000000</v>
+      </c>
+      <c r="D97" s="7" t="n">
+        <v>30556618000000</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 기초 현금및현금성자산 (당기)</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C98" s="7" t="n">
+        <v>27281123000000</v>
+      </c>
+      <c r="D98" s="7" t="n">
+        <v>27281123000000</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 현금흐름표 기초 현금및현금성자산</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C99" s="7" t="n">
+        <v>-10.72</v>
+      </c>
+      <c r="D99" s="7" t="n">
+        <v>-10.72</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 상각후원가측정유가증권의 상환 (전기)</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C100" s="7" t="n">
+        <v>7634677000000</v>
+      </c>
+      <c r="D100" s="7" t="n">
+        <v>7634677000000</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 상각후원가측정유가증권의 상환 (당기)</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C101" s="7" t="n">
+        <v>5900990000000</v>
+      </c>
+      <c r="D101" s="7" t="n">
+        <v>5900990000000</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 현금흐름표 상각후원가측정유가증권의 상환</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C102" s="7" t="n">
+        <v>-22.71</v>
+      </c>
+      <c r="D102" s="7" t="n">
+        <v>-22.71</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 포괄손익계산서 상각후원가측정금융부채 이자비용 (전기)</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C103" s="7" t="n">
+        <v>13127005000000</v>
+      </c>
+      <c r="D103" s="7" t="n">
+        <v>13127005000000</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 포괄손익계산서 상각후원가측정금융부채 이자비용 (당기)</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C104" s="7" t="n">
+        <v>11401953000000</v>
+      </c>
+      <c r="D104" s="7" t="n">
+        <v>11401953000000</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 포괄손익계산서 상각후원가측정금융부채 이자비용</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C105" s="7" t="n">
+        <v>-13.14</v>
+      </c>
+      <c r="D105" s="7" t="n">
+        <v>-13.14</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>스크리닝 완전성(포함됐어야 할 계정 누락 없음)</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C106" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D106" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>스크리닝 정확성(기준 미달 오탐 없음)</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C107" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D107" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/우리금융지주_연결_결과.xlsx
+++ b/우리금융지주_연결_결과.xlsx
@@ -68,6 +68,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -105,18 +106,12 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="1">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00FFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00FF4C4C"/>
+          <fgColor rgb="00FFFF00"/>
+          <bgColor rgb="00FFFF00"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1189,9 +1184,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1201,7 +1196,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -4102,7 +4096,7 @@
   <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
@@ -4116,7 +4110,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -4261,14 +4254,6 @@
       <c r="D11" t="n"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E4:E11">
-    <cfRule type="cellIs" priority="1" operator="greaterThanOrEqual" dxfId="0">
-      <formula>20</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="2" operator="lessThanOrEqual" dxfId="0">
-      <formula>-20</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -4284,7 +4269,7 @@
   <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="91" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
@@ -4304,7 +4289,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
@@ -4312,7 +4296,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
@@ -4375,33 +4358,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="186" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>전기 대비 당기 증감 스크리닝 (분석적 절차)</t>
+          <t>전기 대비 당기 증감 스크리닝</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>[안내] 재무상태표/손익계산서/현금흐름표의 개별 계정 중 전기 대비 증감률이 ±10%를 초과하는 계정만 추립니다(중요성 기준 미만 소액 계정은 제외). 신규계정(전기=0)·부호전환(흑자↔적자)은 %를 계산하지 않고 별도 표시합니다. 증감액(절대금액) 내림차순 정렬이며, ±30% 초과는 진하게, ±10~30%는 연하게 강조됩니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+          <t>[안내] 재무상태표/손익계산서/현금흐름표의 개별 계정 중 전기 대비 증감률이 ±10%를 초과하는 계정만 추립니다(중요성 기준 미만 소액 계정은 제외, 포함 여부는 전기→당기 기준). 신규계정(전기=0)·부호전환(흑자↔적자)은 %를 계산하지 않고 별도 표시합니다. 재무제표구분(재무상태표→손익계산서→현금흐름표) 순으로 묶은 뒤 그 안에서 증감액(절대금액) 내림차순 정렬하며, ±30% 초과인 계정은 '전기→당기 증감률(%)' 칸이 노란색으로 강조됩니다. '구분'이 "증감률초과"인 항목은 통상적으로 계산된 증감률이 기준을 넘었다는 뜻이며(문제가 없다는 뜻이 아님), 신규계정/부호전환은 애초에 %를 계산할 수 없어 별도 분류된 것입니다. '전전기→전기 증감률(%)'은 비교 참고용이며, 두 구간의 증감률 차이가 40%p 이상이면(둘 다 정상 계산된 경우에 한함) '추세이탈'에 표시됩니다 — 단순히 증감률이 큰 게 아니라 이번 기에 갑자기 패턴이 바뀐 계정을 잡아내기 위함입니다.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -4451,7 +4436,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
@@ -4465,25 +4449,40 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
+          <t>전전기금액</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
           <t>전기금액</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>당기금액</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>증감액</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>증감률(%)</t>
-        </is>
-      </c>
       <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>전기→당기 증감률(%)</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>전전기→전기 증감률(%)</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>추세이탈</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
@@ -4501,20 +4500,26 @@
         </is>
       </c>
       <c r="C13" s="8" t="n">
+        <v>498004936000000</v>
+      </c>
+      <c r="D13" s="8" t="n">
         <v>525753320000000</v>
       </c>
-      <c r="D13" s="8" t="n">
+      <c r="E13" s="8" t="n">
         <v>601457286000000</v>
       </c>
-      <c r="E13" s="8" t="n">
+      <c r="F13" s="8" t="n">
         <v>75703966000000</v>
       </c>
-      <c r="F13" s="7" t="n">
+      <c r="G13" s="7" t="n">
         <v>14.4</v>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>정상</t>
+      <c r="H13" s="7" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>증감률초과</t>
         </is>
       </c>
     </row>
@@ -4530,20 +4535,26 @@
         </is>
       </c>
       <c r="C14" s="8" t="n">
+        <v>498004936000000</v>
+      </c>
+      <c r="D14" s="8" t="n">
         <v>525753320000000</v>
       </c>
-      <c r="D14" s="8" t="n">
+      <c r="E14" s="8" t="n">
         <v>601457286000000</v>
       </c>
-      <c r="E14" s="8" t="n">
+      <c r="F14" s="8" t="n">
         <v>75703966000000</v>
       </c>
-      <c r="F14" s="7" t="n">
+      <c r="G14" s="7" t="n">
         <v>14.4</v>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>정상</t>
+      <c r="H14" s="7" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>증감률초과</t>
         </is>
       </c>
     </row>
@@ -4559,20 +4570,26 @@
         </is>
       </c>
       <c r="C15" s="8" t="n">
+        <v>464607446000000</v>
+      </c>
+      <c r="D15" s="8" t="n">
         <v>489858051000000</v>
       </c>
-      <c r="D15" s="8" t="n">
+      <c r="E15" s="8" t="n">
         <v>563598038000000</v>
       </c>
-      <c r="E15" s="8" t="n">
+      <c r="F15" s="8" t="n">
         <v>73739987000000</v>
       </c>
-      <c r="F15" s="7" t="n">
+      <c r="G15" s="7" t="n">
         <v>15.05</v>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>정상</t>
+      <c r="H15" s="7" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>증감률초과</t>
         </is>
       </c>
     </row>
@@ -4591,12 +4608,15 @@
         <v>0</v>
       </c>
       <c r="D16" s="8" t="n">
-        <v>45573864000000</v>
+        <v>0</v>
       </c>
       <c r="E16" s="8" t="n">
         <v>45573864000000</v>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="F16" s="8" t="n">
+        <v>45573864000000</v>
+      </c>
+      <c r="J16" t="inlineStr">
         <is>
           <t>신규계정</t>
         </is>
@@ -4614,156 +4634,211 @@
         </is>
       </c>
       <c r="C17" s="8" t="n">
+        <v>37891495000000</v>
+      </c>
+      <c r="D17" s="8" t="n">
         <v>43797745000000</v>
       </c>
-      <c r="D17" s="8" t="n">
+      <c r="E17" s="8" t="n">
         <v>83499522000000</v>
       </c>
-      <c r="E17" s="8" t="n">
+      <c r="F17" s="8" t="n">
         <v>39701777000000</v>
       </c>
-      <c r="F17" s="7" t="n">
+      <c r="G17" s="7" t="n">
         <v>90.65000000000001</v>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>정상</t>
+      <c r="H17" s="7" t="n">
+        <v>15.59</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>추세이탈</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>증감률초과</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>현금흐름표</t>
+          <t>재무상태표</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>영업활동으로 인한 자산ㆍ부채의 변동</t>
+          <t>현금및현금성자산</t>
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>-13479204000000</v>
+        <v>30556618000000</v>
       </c>
       <c r="D18" s="8" t="n">
-        <v>9225268000000</v>
+        <v>27281123000000</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>22704472000000</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>부호전환</t>
+        <v>38499679000000</v>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>11218556000000</v>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>41.12</v>
+      </c>
+      <c r="H18" s="7" t="n">
+        <v>-10.72</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>추세이탈</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>증감률초과</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>현금흐름표</t>
+          <t>재무상태표</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>영업활동으로 인한 현금흐름</t>
+          <t>당기손익-공정가치측정금융자산</t>
         </is>
       </c>
       <c r="C19" s="8" t="n">
-        <v>-6129300000000</v>
+        <v>21544756000000</v>
       </c>
       <c r="D19" s="8" t="n">
-        <v>13642391000000</v>
+        <v>25202672000000</v>
       </c>
       <c r="E19" s="8" t="n">
-        <v>19771691000000</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>부호전환</t>
+        <v>34245475000000</v>
+      </c>
+      <c r="F19" s="8" t="n">
+        <v>9042803000000</v>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>35.88</v>
+      </c>
+      <c r="H19" s="7" t="n">
+        <v>16.98</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>증감률초과</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>현금흐름표</t>
+          <t>재무상태표</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>현금및현금성자산의 증가(감소)</t>
+          <t>발행사채</t>
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>-3275495000000</v>
+        <v>41239245000000</v>
       </c>
       <c r="D20" s="8" t="n">
-        <v>11218556000000</v>
+        <v>48207103000000</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>14494051000000</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>부호전환</t>
+        <v>55583392000000</v>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>7376289000000</v>
+      </c>
+      <c r="G20" s="7" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="H20" s="7" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>증감률초과</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>현금흐름표</t>
+          <t>재무상태표</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>상각후원가측정대출채권및기타금융자산</t>
+          <t>기타금융부채</t>
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>-21703969000000</v>
+        <v>26115005000000</v>
       </c>
       <c r="D21" s="8" t="n">
-        <v>-8369230000000</v>
+        <v>32314051000000</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>13334739000000</v>
-      </c>
-      <c r="F21" s="7" t="n">
-        <v>61.44</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>정상</t>
+        <v>38118058000000</v>
+      </c>
+      <c r="F21" s="8" t="n">
+        <v>5804007000000</v>
+      </c>
+      <c r="G21" s="7" t="n">
+        <v>17.96</v>
+      </c>
+      <c r="H21" s="7" t="n">
+        <v>23.74</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>증감률초과</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>현금흐름표</t>
+          <t>재무상태표</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>기타포괄손익-공정가치측정금융자산의 취득</t>
+          <t>차입부채</t>
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>31718677000000</v>
+        <v>30986746000000</v>
       </c>
       <c r="D22" s="8" t="n">
-        <v>43073556000000</v>
+        <v>30117031000000</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>11354879000000</v>
-      </c>
-      <c r="F22" s="7" t="n">
-        <v>35.8</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>정상</t>
+        <v>34183267000000</v>
+      </c>
+      <c r="F22" s="8" t="n">
+        <v>4066236000000</v>
+      </c>
+      <c r="G22" s="7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="H22" s="7" t="n">
+        <v>-2.81</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>증감률초과</t>
         </is>
       </c>
     </row>
@@ -4775,53 +4850,70 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>현금및현금성자산</t>
+          <t>당기손익-공정가치측정금융부채</t>
         </is>
       </c>
       <c r="C23" s="8" t="n">
-        <v>27281123000000</v>
+        <v>6138313000000</v>
       </c>
       <c r="D23" s="8" t="n">
-        <v>38499679000000</v>
+        <v>9896597000000</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>11218556000000</v>
-      </c>
-      <c r="F23" s="7" t="n">
-        <v>41.12</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>정상</t>
+        <v>6356934000000</v>
+      </c>
+      <c r="F23" s="8" t="n">
+        <v>-3539663000000</v>
+      </c>
+      <c r="G23" s="7" t="n">
+        <v>-35.77</v>
+      </c>
+      <c r="H23" s="7" t="n">
+        <v>61.23</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>추세이탈</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>증감률초과</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>현금흐름표</t>
+          <t>포괄손익계산서</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>현금및현금성자산</t>
+          <t>상각후원가측정금융부채 이자비용</t>
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>27281123000000</v>
+        <v>11899014000000</v>
       </c>
       <c r="D24" s="8" t="n">
-        <v>38499679000000</v>
+        <v>13127005000000</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>11218556000000</v>
-      </c>
-      <c r="F24" s="7" t="n">
-        <v>41.12</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>정상</t>
+        <v>11401953000000</v>
+      </c>
+      <c r="F24" s="8" t="n">
+        <v>-1725052000000</v>
+      </c>
+      <c r="G24" s="7" t="n">
+        <v>-13.14</v>
+      </c>
+      <c r="H24" s="7" t="n">
+        <v>10.32</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>증감률초과</t>
         </is>
       </c>
     </row>
@@ -4833,24 +4925,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>예수부채</t>
+          <t>영업활동으로 인한 자산ㆍ부채의 변동</t>
         </is>
       </c>
       <c r="C25" s="8" t="n">
-        <v>3411535000000</v>
+        <v>-4116666000000</v>
       </c>
       <c r="D25" s="8" t="n">
-        <v>13839807000000</v>
+        <v>-13479204000000</v>
       </c>
       <c r="E25" s="8" t="n">
-        <v>10428272000000</v>
-      </c>
-      <c r="F25" s="7" t="n">
-        <v>305.68</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>정상</t>
+        <v>9225268000000</v>
+      </c>
+      <c r="F25" s="8" t="n">
+        <v>22704472000000</v>
+      </c>
+      <c r="H25" s="7" t="n">
+        <v>-227.43</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>부호전환</t>
         </is>
       </c>
     </row>
@@ -4862,53 +4957,56 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>투자활동으로 인한 현금흐름</t>
+          <t>영업활동으로 인한 현금흐름</t>
         </is>
       </c>
       <c r="C26" s="8" t="n">
-        <v>-34299000000</v>
+        <v>1621942000000</v>
       </c>
       <c r="D26" s="8" t="n">
-        <v>-9880603000000</v>
+        <v>-6129300000000</v>
       </c>
       <c r="E26" s="8" t="n">
-        <v>-9846304000000</v>
-      </c>
-      <c r="F26" s="7" t="n">
-        <v>-28707.26</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>정상</t>
+        <v>13642391000000</v>
+      </c>
+      <c r="F26" s="8" t="n">
+        <v>19771691000000</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>부호전환</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>재무상태표</t>
+          <t>현금흐름표</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>당기손익-공정가치측정금융자산</t>
+          <t>현금및현금성자산의 증가(감소)</t>
         </is>
       </c>
       <c r="C27" s="8" t="n">
-        <v>25202672000000</v>
+        <v>-3662530000000</v>
       </c>
       <c r="D27" s="8" t="n">
-        <v>34245475000000</v>
+        <v>-3275495000000</v>
       </c>
       <c r="E27" s="8" t="n">
-        <v>9042803000000</v>
-      </c>
-      <c r="F27" s="7" t="n">
-        <v>35.88</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>정상</t>
+        <v>11218556000000</v>
+      </c>
+      <c r="F27" s="8" t="n">
+        <v>14494051000000</v>
+      </c>
+      <c r="H27" s="7" t="n">
+        <v>10.57</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>부호전환</t>
         </is>
       </c>
     </row>
@@ -4920,24 +5018,35 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>당기손익-공정가치측정금융상품의 취득</t>
+          <t>상각후원가측정대출채권및기타금융자산</t>
         </is>
       </c>
       <c r="C28" s="8" t="n">
-        <v>11111809000000</v>
+        <v>-18598117000000</v>
       </c>
       <c r="D28" s="8" t="n">
-        <v>20087654000000</v>
+        <v>-21703969000000</v>
       </c>
       <c r="E28" s="8" t="n">
-        <v>8975845000000</v>
-      </c>
-      <c r="F28" s="7" t="n">
-        <v>80.78</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>정상</t>
+        <v>-8369230000000</v>
+      </c>
+      <c r="F28" s="8" t="n">
+        <v>13334739000000</v>
+      </c>
+      <c r="G28" s="7" t="n">
+        <v>61.44</v>
+      </c>
+      <c r="H28" s="7" t="n">
+        <v>-16.7</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>추세이탈</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>증감률초과</t>
         </is>
       </c>
     </row>
@@ -4949,24 +5058,30 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>기타포괄손익-공정가치측정금융자산의 처분</t>
+          <t>기타포괄손익-공정가치측정금융자산의 취득</t>
         </is>
       </c>
       <c r="C29" s="8" t="n">
-        <v>26921313000000</v>
+        <v>24211531000000</v>
       </c>
       <c r="D29" s="8" t="n">
-        <v>35153473000000</v>
+        <v>31718677000000</v>
       </c>
       <c r="E29" s="8" t="n">
-        <v>8232160000000</v>
-      </c>
-      <c r="F29" s="7" t="n">
-        <v>30.58</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>정상</t>
+        <v>43073556000000</v>
+      </c>
+      <c r="F29" s="8" t="n">
+        <v>11354879000000</v>
+      </c>
+      <c r="G29" s="7" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="H29" s="7" t="n">
+        <v>31.01</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>증감률초과</t>
         </is>
       </c>
     </row>
@@ -4978,53 +5093,75 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>당기손익-공정가치측정금융상품의 처분</t>
+          <t>현금및현금성자산</t>
         </is>
       </c>
       <c r="C30" s="8" t="n">
-        <v>11659750000000</v>
+        <v>30556618000000</v>
       </c>
       <c r="D30" s="8" t="n">
-        <v>19103867000000</v>
+        <v>27281123000000</v>
       </c>
       <c r="E30" s="8" t="n">
-        <v>7444117000000</v>
-      </c>
-      <c r="F30" s="7" t="n">
-        <v>63.84</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>정상</t>
+        <v>38499679000000</v>
+      </c>
+      <c r="F30" s="8" t="n">
+        <v>11218556000000</v>
+      </c>
+      <c r="G30" s="7" t="n">
+        <v>41.12</v>
+      </c>
+      <c r="H30" s="7" t="n">
+        <v>-10.72</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>추세이탈</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>증감률초과</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>재무상태표</t>
+          <t>현금흐름표</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>발행사채</t>
+          <t>예수부채</t>
         </is>
       </c>
       <c r="C31" s="8" t="n">
-        <v>48207103000000</v>
+        <v>15176465000000</v>
       </c>
       <c r="D31" s="8" t="n">
-        <v>55583392000000</v>
+        <v>3411535000000</v>
       </c>
       <c r="E31" s="8" t="n">
-        <v>7376289000000</v>
-      </c>
-      <c r="F31" s="7" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>정상</t>
+        <v>13839807000000</v>
+      </c>
+      <c r="F31" s="8" t="n">
+        <v>10428272000000</v>
+      </c>
+      <c r="G31" s="7" t="n">
+        <v>305.68</v>
+      </c>
+      <c r="H31" s="7" t="n">
+        <v>-77.52</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>추세이탈</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>증감률초과</t>
         </is>
       </c>
     </row>
@@ -5036,82 +5173,110 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>재무활동으로 인한 현금흐름</t>
+          <t>투자활동으로 인한 현금흐름</t>
         </is>
       </c>
       <c r="C32" s="8" t="n">
-        <v>1245341000000</v>
+        <v>-2254141000000</v>
       </c>
       <c r="D32" s="8" t="n">
-        <v>7685336000000</v>
+        <v>-34299000000</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>6439995000000</v>
-      </c>
-      <c r="F32" s="7" t="n">
-        <v>517.13</v>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>정상</t>
+        <v>-9880603000000</v>
+      </c>
+      <c r="F32" s="8" t="n">
+        <v>-9846304000000</v>
+      </c>
+      <c r="G32" s="7" t="n">
+        <v>-28707.26</v>
+      </c>
+      <c r="H32" s="7" t="n">
+        <v>98.48</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>추세이탈</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>증감률초과</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>재무상태표</t>
+          <t>현금흐름표</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>기타금융부채</t>
+          <t>당기손익-공정가치측정금융상품의 취득</t>
         </is>
       </c>
       <c r="C33" s="8" t="n">
-        <v>32314051000000</v>
+        <v>12167823000000</v>
       </c>
       <c r="D33" s="8" t="n">
-        <v>38118058000000</v>
+        <v>11111809000000</v>
       </c>
       <c r="E33" s="8" t="n">
-        <v>5804007000000</v>
-      </c>
-      <c r="F33" s="7" t="n">
-        <v>17.96</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>정상</t>
+        <v>20087654000000</v>
+      </c>
+      <c r="F33" s="8" t="n">
+        <v>8975845000000</v>
+      </c>
+      <c r="G33" s="7" t="n">
+        <v>80.78</v>
+      </c>
+      <c r="H33" s="7" t="n">
+        <v>-8.68</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>추세이탈</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>증감률초과</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>재무상태표</t>
+          <t>현금흐름표</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>차입부채</t>
+          <t>기타포괄손익-공정가치측정금융자산의 처분</t>
         </is>
       </c>
       <c r="C34" s="8" t="n">
-        <v>30117031000000</v>
+        <v>20648897000000</v>
       </c>
       <c r="D34" s="8" t="n">
-        <v>34183267000000</v>
+        <v>26921313000000</v>
       </c>
       <c r="E34" s="8" t="n">
-        <v>4066236000000</v>
-      </c>
-      <c r="F34" s="7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>정상</t>
+        <v>35153473000000</v>
+      </c>
+      <c r="F34" s="8" t="n">
+        <v>8232160000000</v>
+      </c>
+      <c r="G34" s="7" t="n">
+        <v>30.58</v>
+      </c>
+      <c r="H34" s="7" t="n">
+        <v>30.38</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>증감률초과</t>
         </is>
       </c>
     </row>
@@ -5123,53 +5288,67 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>발행사채의 상환</t>
+          <t>당기손익-공정가치측정금융상품의 처분</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
-        <v>35473345000000</v>
+        <v>10487513000000</v>
       </c>
       <c r="D35" s="8" t="n">
-        <v>31611225000000</v>
+        <v>11659750000000</v>
       </c>
       <c r="E35" s="8" t="n">
-        <v>-3862120000000</v>
-      </c>
-      <c r="F35" s="7" t="n">
-        <v>-10.89</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>정상</t>
+        <v>19103867000000</v>
+      </c>
+      <c r="F35" s="8" t="n">
+        <v>7444117000000</v>
+      </c>
+      <c r="G35" s="7" t="n">
+        <v>63.84</v>
+      </c>
+      <c r="H35" s="7" t="n">
+        <v>11.18</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>추세이탈</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>증감률초과</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>재무상태표</t>
+          <t>현금흐름표</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>당기손익-공정가치측정금융부채</t>
+          <t>재무활동으로 인한 현금흐름</t>
         </is>
       </c>
       <c r="C36" s="8" t="n">
-        <v>9896597000000</v>
+        <v>-2860177000000</v>
       </c>
       <c r="D36" s="8" t="n">
-        <v>6356934000000</v>
+        <v>1245341000000</v>
       </c>
       <c r="E36" s="8" t="n">
-        <v>-3539663000000</v>
-      </c>
-      <c r="F36" s="7" t="n">
-        <v>-35.77</v>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>정상</t>
+        <v>7685336000000</v>
+      </c>
+      <c r="F36" s="8" t="n">
+        <v>6439995000000</v>
+      </c>
+      <c r="G36" s="7" t="n">
+        <v>517.13</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>증감률초과</t>
         </is>
       </c>
     </row>
@@ -5181,24 +5360,30 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>기초 현금및현금성자산</t>
+          <t>발행사채의 상환</t>
         </is>
       </c>
       <c r="C37" s="8" t="n">
-        <v>30556618000000</v>
+        <v>34329491000000</v>
       </c>
       <c r="D37" s="8" t="n">
-        <v>27281123000000</v>
+        <v>35473345000000</v>
       </c>
       <c r="E37" s="8" t="n">
-        <v>-3275495000000</v>
-      </c>
-      <c r="F37" s="7" t="n">
-        <v>-10.72</v>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>정상</t>
+        <v>31611225000000</v>
+      </c>
+      <c r="F37" s="8" t="n">
+        <v>-3862120000000</v>
+      </c>
+      <c r="G37" s="7" t="n">
+        <v>-10.89</v>
+      </c>
+      <c r="H37" s="7" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>증감률초과</t>
         </is>
       </c>
     </row>
@@ -5210,71 +5395,75 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>상각후원가측정유가증권의 상환</t>
+          <t>기초 현금및현금성자산</t>
         </is>
       </c>
       <c r="C38" s="8" t="n">
-        <v>7634677000000</v>
+        <v>34219148000000</v>
       </c>
       <c r="D38" s="8" t="n">
-        <v>5900990000000</v>
+        <v>30556618000000</v>
       </c>
       <c r="E38" s="8" t="n">
-        <v>-1733687000000</v>
-      </c>
-      <c r="F38" s="7" t="n">
-        <v>-22.71</v>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>정상</t>
+        <v>27281123000000</v>
+      </c>
+      <c r="F38" s="8" t="n">
+        <v>-3275495000000</v>
+      </c>
+      <c r="G38" s="7" t="n">
+        <v>-10.72</v>
+      </c>
+      <c r="H38" s="7" t="n">
+        <v>-10.7</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>증감률초과</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>포괄손익계산서</t>
+          <t>현금흐름표</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>상각후원가측정금융부채 이자비용</t>
+          <t>상각후원가측정유가증권의 상환</t>
         </is>
       </c>
       <c r="C39" s="8" t="n">
-        <v>13127005000000</v>
+        <v>8727124000000</v>
       </c>
       <c r="D39" s="8" t="n">
-        <v>11401953000000</v>
+        <v>7634677000000</v>
       </c>
       <c r="E39" s="8" t="n">
-        <v>-1725052000000</v>
-      </c>
-      <c r="F39" s="7" t="n">
-        <v>-13.14</v>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>정상</t>
+        <v>5900990000000</v>
+      </c>
+      <c r="F39" s="8" t="n">
+        <v>-1733687000000</v>
+      </c>
+      <c r="G39" s="7" t="n">
+        <v>-22.71</v>
+      </c>
+      <c r="H39" s="7" t="n">
+        <v>-12.52</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>증감률초과</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="F13:F39">
-    <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="1">
+  <conditionalFormatting sqref="G13:G39">
+    <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
       <formula>30.0</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="1">
+    <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="0">
       <formula>-30.0</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="3" operator="between" dxfId="0">
-      <formula>10.0</formula>
-      <formula>30.0</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="4" operator="between" dxfId="0">
-      <formula>-30.0</formula>
-      <formula>-10.0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5287,13 +5476,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E107"/>
+  <dimension ref="A1:E185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="125" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -5311,15 +5500,13 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>✓ 전체 92건 모두 일치 (검증 통과)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5"/>
+          <t>✓ 전체 170건 모두 일치 (검증 통과)</t>
+        </is>
+      </c>
+    </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -5636,19 +5823,19 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 재무상태표 부채와자본총계 (전기)</t>
+          <t>[스크리닝-원본금액] 재무상태표 부채와자본총계 (전전기)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>전기</t>
+          <t>전전기</t>
         </is>
       </c>
       <c r="C25" s="7" t="n">
-        <v>525753320000000</v>
+        <v>498004936000000</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>525753320000000</v>
+        <v>498004936000000</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -5659,19 +5846,19 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 재무상태표 부채와자본총계 (당기)</t>
+          <t>[스크리닝-원본금액] 재무상태표 부채와자본총계 (전기)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>전기</t>
         </is>
       </c>
       <c r="C26" s="7" t="n">
-        <v>601457286000000</v>
+        <v>525753320000000</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>601457286000000</v>
+        <v>525753320000000</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -5682,19 +5869,19 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>[스크리닝-증감률] 재무상태표 부채와자본총계</t>
+          <t>[스크리닝-원본금액] 재무상태표 부채와자본총계 (당기)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>전기→당기</t>
+          <t>당기</t>
         </is>
       </c>
       <c r="C27" s="7" t="n">
-        <v>14.4</v>
+        <v>601457286000000</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>14.4</v>
+        <v>601457286000000</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -5705,19 +5892,19 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 재무상태표 자산총계 (전기)</t>
+          <t>[스크리닝-증감률] 재무상태표 부채와자본총계</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>전기</t>
+          <t>전기→당기</t>
         </is>
       </c>
       <c r="C28" s="7" t="n">
-        <v>525753320000000</v>
+        <v>14.4</v>
       </c>
       <c r="D28" s="7" t="n">
-        <v>525753320000000</v>
+        <v>14.4</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -5728,19 +5915,19 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 재무상태표 자산총계 (당기)</t>
+          <t>[스크리닝-전전기증감률] 재무상태표 부채와자본총계</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>전전기→전기</t>
         </is>
       </c>
       <c r="C29" s="7" t="n">
-        <v>601457286000000</v>
+        <v>5.57</v>
       </c>
       <c r="D29" s="7" t="n">
-        <v>601457286000000</v>
+        <v>5.57</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -5751,19 +5938,19 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>[스크리닝-증감률] 재무상태표 자산총계</t>
+          <t>[스크리닝-추세이탈] 재무상태표 부채와자본총계</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>전기→당기</t>
+          <t>추세이탈판정</t>
         </is>
       </c>
       <c r="C30" s="7" t="n">
-        <v>14.4</v>
+        <v>0</v>
       </c>
       <c r="D30" s="7" t="n">
-        <v>14.4</v>
+        <v>0</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -5774,19 +5961,19 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 재무상태표 부채총계 (전기)</t>
+          <t>[스크리닝-원본금액] 재무상태표 자산총계 (전전기)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>전기</t>
+          <t>전전기</t>
         </is>
       </c>
       <c r="C31" s="7" t="n">
-        <v>489858051000000</v>
+        <v>498004936000000</v>
       </c>
       <c r="D31" s="7" t="n">
-        <v>489858051000000</v>
+        <v>498004936000000</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -5797,19 +5984,19 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 재무상태표 부채총계 (당기)</t>
+          <t>[스크리닝-원본금액] 재무상태표 자산총계 (전기)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>전기</t>
         </is>
       </c>
       <c r="C32" s="7" t="n">
-        <v>563598038000000</v>
+        <v>525753320000000</v>
       </c>
       <c r="D32" s="7" t="n">
-        <v>563598038000000</v>
+        <v>525753320000000</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -5820,19 +6007,19 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>[스크리닝-증감률] 재무상태표 부채총계</t>
+          <t>[스크리닝-원본금액] 재무상태표 자산총계 (당기)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>전기→당기</t>
+          <t>당기</t>
         </is>
       </c>
       <c r="C33" s="7" t="n">
-        <v>15.05</v>
+        <v>601457286000000</v>
       </c>
       <c r="D33" s="7" t="n">
-        <v>15.05</v>
+        <v>601457286000000</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -5843,19 +6030,19 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 재무상태표 보험계약부채 (전기)</t>
+          <t>[스크리닝-증감률] 재무상태표 자산총계</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>전기</t>
+          <t>전기→당기</t>
         </is>
       </c>
       <c r="C34" s="7" t="n">
-        <v>0</v>
+        <v>14.4</v>
       </c>
       <c r="D34" s="7" t="n">
-        <v>0</v>
+        <v>14.4</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -5866,19 +6053,19 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 재무상태표 보험계약부채 (당기)</t>
+          <t>[스크리닝-전전기증감률] 재무상태표 자산총계</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>전전기→전기</t>
         </is>
       </c>
       <c r="C35" s="7" t="n">
-        <v>45573864000000</v>
+        <v>5.57</v>
       </c>
       <c r="D35" s="7" t="n">
-        <v>45573864000000</v>
+        <v>5.57</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -5889,19 +6076,19 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>[스크리닝-분류:신규계정] 재무상태표 보험계약부채</t>
+          <t>[스크리닝-추세이탈] 재무상태표 자산총계</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>전기→당기</t>
+          <t>추세이탈판정</t>
         </is>
       </c>
       <c r="C36" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D36" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -5912,19 +6099,19 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 재무상태표 기타포괄손익-공정가치측정금융자산 (전기)</t>
+          <t>[스크리닝-원본금액] 재무상태표 부채총계 (전전기)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>전기</t>
+          <t>전전기</t>
         </is>
       </c>
       <c r="C37" s="7" t="n">
-        <v>43797745000000</v>
+        <v>464607446000000</v>
       </c>
       <c r="D37" s="7" t="n">
-        <v>43797745000000</v>
+        <v>464607446000000</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -5935,19 +6122,19 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 재무상태표 기타포괄손익-공정가치측정금융자산 (당기)</t>
+          <t>[스크리닝-원본금액] 재무상태표 부채총계 (전기)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>전기</t>
         </is>
       </c>
       <c r="C38" s="7" t="n">
-        <v>83499522000000</v>
+        <v>489858051000000</v>
       </c>
       <c r="D38" s="7" t="n">
-        <v>83499522000000</v>
+        <v>489858051000000</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -5958,19 +6145,19 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>[스크리닝-증감률] 재무상태표 기타포괄손익-공정가치측정금융자산</t>
+          <t>[스크리닝-원본금액] 재무상태표 부채총계 (당기)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>전기→당기</t>
+          <t>당기</t>
         </is>
       </c>
       <c r="C39" s="7" t="n">
-        <v>90.65000000000001</v>
+        <v>563598038000000</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>90.65000000000001</v>
+        <v>563598038000000</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -5981,19 +6168,19 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 현금흐름표 영업활동으로 인한 자산ㆍ부채의 변동 (전기)</t>
+          <t>[스크리닝-증감률] 재무상태표 부채총계</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>전기</t>
+          <t>전기→당기</t>
         </is>
       </c>
       <c r="C40" s="7" t="n">
-        <v>-13479204000000</v>
+        <v>15.05</v>
       </c>
       <c r="D40" s="7" t="n">
-        <v>-13479204000000</v>
+        <v>15.05</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -6004,19 +6191,19 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 현금흐름표 영업활동으로 인한 자산ㆍ부채의 변동 (당기)</t>
+          <t>[스크리닝-전전기증감률] 재무상태표 부채총계</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>전전기→전기</t>
         </is>
       </c>
       <c r="C41" s="7" t="n">
-        <v>9225268000000</v>
+        <v>5.43</v>
       </c>
       <c r="D41" s="7" t="n">
-        <v>9225268000000</v>
+        <v>5.43</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -6027,19 +6214,19 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>[스크리닝-분류:부호전환] 현금흐름표 영업활동으로 인한 자산ㆍ부채의 변동</t>
+          <t>[스크리닝-추세이탈] 재무상태표 부채총계</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>전기→당기</t>
+          <t>추세이탈판정</t>
         </is>
       </c>
       <c r="C42" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D42" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -6050,19 +6237,19 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 현금흐름표 영업활동으로 인한 현금흐름 (전기)</t>
+          <t>[스크리닝-원본금액] 재무상태표 보험계약부채 (전전기)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>전기</t>
+          <t>전전기</t>
         </is>
       </c>
       <c r="C43" s="7" t="n">
-        <v>-6129300000000</v>
+        <v>0</v>
       </c>
       <c r="D43" s="7" t="n">
-        <v>-6129300000000</v>
+        <v>0</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -6073,19 +6260,19 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 현금흐름표 영업활동으로 인한 현금흐름 (당기)</t>
+          <t>[스크리닝-원본금액] 재무상태표 보험계약부채 (전기)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>전기</t>
         </is>
       </c>
       <c r="C44" s="7" t="n">
-        <v>13642391000000</v>
+        <v>0</v>
       </c>
       <c r="D44" s="7" t="n">
-        <v>13642391000000</v>
+        <v>0</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -6096,19 +6283,19 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>[스크리닝-분류:부호전환] 현금흐름표 영업활동으로 인한 현금흐름</t>
+          <t>[스크리닝-원본금액] 재무상태표 보험계약부채 (당기)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>전기→당기</t>
+          <t>당기</t>
         </is>
       </c>
       <c r="C45" s="7" t="n">
-        <v>1</v>
+        <v>45573864000000</v>
       </c>
       <c r="D45" s="7" t="n">
-        <v>1</v>
+        <v>45573864000000</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -6119,19 +6306,19 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 현금흐름표 현금및현금성자산의 증가(감소) (전기)</t>
+          <t>[스크리닝-분류:신규계정] 재무상태표 보험계약부채</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>전기</t>
+          <t>전기→당기</t>
         </is>
       </c>
       <c r="C46" s="7" t="n">
-        <v>-3275495000000</v>
+        <v>1</v>
       </c>
       <c r="D46" s="7" t="n">
-        <v>-3275495000000</v>
+        <v>1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -6142,19 +6329,19 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 현금흐름표 현금및현금성자산의 증가(감소) (당기)</t>
+          <t>[스크리닝-추세이탈] 재무상태표 보험계약부채</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>추세이탈판정</t>
         </is>
       </c>
       <c r="C47" s="7" t="n">
-        <v>11218556000000</v>
+        <v>0</v>
       </c>
       <c r="D47" s="7" t="n">
-        <v>11218556000000</v>
+        <v>0</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -6165,19 +6352,19 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>[스크리닝-분류:부호전환] 현금흐름표 현금및현금성자산의 증가(감소)</t>
+          <t>[스크리닝-원본금액] 재무상태표 기타포괄손익-공정가치측정금융자산 (전전기)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>전기→당기</t>
+          <t>전전기</t>
         </is>
       </c>
       <c r="C48" s="7" t="n">
-        <v>1</v>
+        <v>37891495000000</v>
       </c>
       <c r="D48" s="7" t="n">
-        <v>1</v>
+        <v>37891495000000</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -6188,7 +6375,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 현금흐름표 상각후원가측정대출채권및기타금융자산 (전기)</t>
+          <t>[스크리닝-원본금액] 재무상태표 기타포괄손익-공정가치측정금융자산 (전기)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6197,10 +6384,10 @@
         </is>
       </c>
       <c r="C49" s="7" t="n">
-        <v>-21703969000000</v>
+        <v>43797745000000</v>
       </c>
       <c r="D49" s="7" t="n">
-        <v>-21703969000000</v>
+        <v>43797745000000</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -6211,7 +6398,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 현금흐름표 상각후원가측정대출채권및기타금융자산 (당기)</t>
+          <t>[스크리닝-원본금액] 재무상태표 기타포괄손익-공정가치측정금융자산 (당기)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6220,10 +6407,10 @@
         </is>
       </c>
       <c r="C50" s="7" t="n">
-        <v>-8369230000000</v>
+        <v>83499522000000</v>
       </c>
       <c r="D50" s="7" t="n">
-        <v>-8369230000000</v>
+        <v>83499522000000</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -6234,7 +6421,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>[스크리닝-증감률] 현금흐름표 상각후원가측정대출채권및기타금융자산</t>
+          <t>[스크리닝-증감률] 재무상태표 기타포괄손익-공정가치측정금융자산</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6243,10 +6430,10 @@
         </is>
       </c>
       <c r="C51" s="7" t="n">
-        <v>61.44</v>
+        <v>90.65000000000001</v>
       </c>
       <c r="D51" s="7" t="n">
-        <v>61.44</v>
+        <v>90.65000000000001</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -6257,19 +6444,19 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 현금흐름표 기타포괄손익-공정가치측정금융자산의 취득 (전기)</t>
+          <t>[스크리닝-전전기증감률] 재무상태표 기타포괄손익-공정가치측정금융자산</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>전기</t>
+          <t>전전기→전기</t>
         </is>
       </c>
       <c r="C52" s="7" t="n">
-        <v>31718677000000</v>
+        <v>15.59</v>
       </c>
       <c r="D52" s="7" t="n">
-        <v>31718677000000</v>
+        <v>15.59</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -6280,19 +6467,19 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 현금흐름표 기타포괄손익-공정가치측정금융자산의 취득 (당기)</t>
+          <t>[스크리닝-추세이탈] 재무상태표 기타포괄손익-공정가치측정금융자산</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>추세이탈판정</t>
         </is>
       </c>
       <c r="C53" s="7" t="n">
-        <v>43073556000000</v>
+        <v>1</v>
       </c>
       <c r="D53" s="7" t="n">
-        <v>43073556000000</v>
+        <v>1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -6303,19 +6490,19 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>[스크리닝-증감률] 현금흐름표 기타포괄손익-공정가치측정금융자산의 취득</t>
+          <t>[스크리닝-원본금액] 재무상태표 현금및현금성자산 (전전기)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>전기→당기</t>
+          <t>전전기</t>
         </is>
       </c>
       <c r="C54" s="7" t="n">
-        <v>35.8</v>
+        <v>30556618000000</v>
       </c>
       <c r="D54" s="7" t="n">
-        <v>35.8</v>
+        <v>30556618000000</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -6395,19 +6582,19 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 현금흐름표 현금및현금성자산 (전기)</t>
+          <t>[스크리닝-전전기증감률] 재무상태표 현금및현금성자산</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>전기</t>
+          <t>전전기→전기</t>
         </is>
       </c>
       <c r="C58" s="7" t="n">
-        <v>27281123000000</v>
+        <v>-10.72</v>
       </c>
       <c r="D58" s="7" t="n">
-        <v>27281123000000</v>
+        <v>-10.72</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -6418,19 +6605,19 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 현금흐름표 현금및현금성자산 (당기)</t>
+          <t>[스크리닝-추세이탈] 재무상태표 현금및현금성자산</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>추세이탈판정</t>
         </is>
       </c>
       <c r="C59" s="7" t="n">
-        <v>38499679000000</v>
+        <v>1</v>
       </c>
       <c r="D59" s="7" t="n">
-        <v>38499679000000</v>
+        <v>1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -6441,19 +6628,19 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>[스크리닝-증감률] 현금흐름표 현금및현금성자산</t>
+          <t>[스크리닝-원본금액] 재무상태표 당기손익-공정가치측정금융자산 (전전기)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>전기→당기</t>
+          <t>전전기</t>
         </is>
       </c>
       <c r="C60" s="7" t="n">
-        <v>41.12</v>
+        <v>21544756000000</v>
       </c>
       <c r="D60" s="7" t="n">
-        <v>41.12</v>
+        <v>21544756000000</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -6464,7 +6651,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 현금흐름표 예수부채 (전기)</t>
+          <t>[스크리닝-원본금액] 재무상태표 당기손익-공정가치측정금융자산 (전기)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6473,10 +6660,10 @@
         </is>
       </c>
       <c r="C61" s="7" t="n">
-        <v>3411535000000</v>
+        <v>25202672000000</v>
       </c>
       <c r="D61" s="7" t="n">
-        <v>3411535000000</v>
+        <v>25202672000000</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -6487,7 +6674,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 현금흐름표 예수부채 (당기)</t>
+          <t>[스크리닝-원본금액] 재무상태표 당기손익-공정가치측정금융자산 (당기)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6496,10 +6683,10 @@
         </is>
       </c>
       <c r="C62" s="7" t="n">
-        <v>13839807000000</v>
+        <v>34245475000000</v>
       </c>
       <c r="D62" s="7" t="n">
-        <v>13839807000000</v>
+        <v>34245475000000</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -6510,7 +6697,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>[스크리닝-증감률] 현금흐름표 예수부채</t>
+          <t>[스크리닝-증감률] 재무상태표 당기손익-공정가치측정금융자산</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6519,10 +6706,10 @@
         </is>
       </c>
       <c r="C63" s="7" t="n">
-        <v>305.68</v>
+        <v>35.88</v>
       </c>
       <c r="D63" s="7" t="n">
-        <v>305.68</v>
+        <v>35.88</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -6533,19 +6720,19 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 현금흐름표 투자활동으로 인한 현금흐름 (전기)</t>
+          <t>[스크리닝-전전기증감률] 재무상태표 당기손익-공정가치측정금융자산</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>전기</t>
+          <t>전전기→전기</t>
         </is>
       </c>
       <c r="C64" s="7" t="n">
-        <v>-34299000000</v>
+        <v>16.98</v>
       </c>
       <c r="D64" s="7" t="n">
-        <v>-34299000000</v>
+        <v>16.98</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -6556,19 +6743,19 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 현금흐름표 투자활동으로 인한 현금흐름 (당기)</t>
+          <t>[스크리닝-추세이탈] 재무상태표 당기손익-공정가치측정금융자산</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>추세이탈판정</t>
         </is>
       </c>
       <c r="C65" s="7" t="n">
-        <v>-9880603000000</v>
+        <v>0</v>
       </c>
       <c r="D65" s="7" t="n">
-        <v>-9880603000000</v>
+        <v>0</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -6579,19 +6766,19 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>[스크리닝-증감률] 현금흐름표 투자활동으로 인한 현금흐름</t>
+          <t>[스크리닝-원본금액] 재무상태표 발행사채 (전전기)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>전기→당기</t>
+          <t>전전기</t>
         </is>
       </c>
       <c r="C66" s="7" t="n">
-        <v>-28707.26</v>
+        <v>41239245000000</v>
       </c>
       <c r="D66" s="7" t="n">
-        <v>-28707.26</v>
+        <v>41239245000000</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -6602,7 +6789,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 재무상태표 당기손익-공정가치측정금융자산 (전기)</t>
+          <t>[스크리닝-원본금액] 재무상태표 발행사채 (전기)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6611,10 +6798,10 @@
         </is>
       </c>
       <c r="C67" s="7" t="n">
-        <v>25202672000000</v>
+        <v>48207103000000</v>
       </c>
       <c r="D67" s="7" t="n">
-        <v>25202672000000</v>
+        <v>48207103000000</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -6625,7 +6812,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 재무상태표 당기손익-공정가치측정금융자산 (당기)</t>
+          <t>[스크리닝-원본금액] 재무상태표 발행사채 (당기)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6634,10 +6821,10 @@
         </is>
       </c>
       <c r="C68" s="7" t="n">
-        <v>34245475000000</v>
+        <v>55583392000000</v>
       </c>
       <c r="D68" s="7" t="n">
-        <v>34245475000000</v>
+        <v>55583392000000</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -6648,7 +6835,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>[스크리닝-증감률] 재무상태표 당기손익-공정가치측정금융자산</t>
+          <t>[스크리닝-증감률] 재무상태표 발행사채</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6657,10 +6844,10 @@
         </is>
       </c>
       <c r="C69" s="7" t="n">
-        <v>35.88</v>
+        <v>15.3</v>
       </c>
       <c r="D69" s="7" t="n">
-        <v>35.88</v>
+        <v>15.3</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -6671,19 +6858,19 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 현금흐름표 당기손익-공정가치측정금융상품의 취득 (전기)</t>
+          <t>[스크리닝-전전기증감률] 재무상태표 발행사채</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>전기</t>
+          <t>전전기→전기</t>
         </is>
       </c>
       <c r="C70" s="7" t="n">
-        <v>11111809000000</v>
+        <v>16.9</v>
       </c>
       <c r="D70" s="7" t="n">
-        <v>11111809000000</v>
+        <v>16.9</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -6694,19 +6881,19 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 현금흐름표 당기손익-공정가치측정금융상품의 취득 (당기)</t>
+          <t>[스크리닝-추세이탈] 재무상태표 발행사채</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>추세이탈판정</t>
         </is>
       </c>
       <c r="C71" s="7" t="n">
-        <v>20087654000000</v>
+        <v>0</v>
       </c>
       <c r="D71" s="7" t="n">
-        <v>20087654000000</v>
+        <v>0</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -6717,19 +6904,19 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>[스크리닝-증감률] 현금흐름표 당기손익-공정가치측정금융상품의 취득</t>
+          <t>[스크리닝-원본금액] 재무상태표 기타금융부채 (전전기)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>전기→당기</t>
+          <t>전전기</t>
         </is>
       </c>
       <c r="C72" s="7" t="n">
-        <v>80.78</v>
+        <v>26115005000000</v>
       </c>
       <c r="D72" s="7" t="n">
-        <v>80.78</v>
+        <v>26115005000000</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -6740,7 +6927,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 현금흐름표 기타포괄손익-공정가치측정금융자산의 처분 (전기)</t>
+          <t>[스크리닝-원본금액] 재무상태표 기타금융부채 (전기)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6749,10 +6936,10 @@
         </is>
       </c>
       <c r="C73" s="7" t="n">
-        <v>26921313000000</v>
+        <v>32314051000000</v>
       </c>
       <c r="D73" s="7" t="n">
-        <v>26921313000000</v>
+        <v>32314051000000</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -6763,7 +6950,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 현금흐름표 기타포괄손익-공정가치측정금융자산의 처분 (당기)</t>
+          <t>[스크리닝-원본금액] 재무상태표 기타금융부채 (당기)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6772,10 +6959,10 @@
         </is>
       </c>
       <c r="C74" s="7" t="n">
-        <v>35153473000000</v>
+        <v>38118058000000</v>
       </c>
       <c r="D74" s="7" t="n">
-        <v>35153473000000</v>
+        <v>38118058000000</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -6786,7 +6973,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>[스크리닝-증감률] 현금흐름표 기타포괄손익-공정가치측정금융자산의 처분</t>
+          <t>[스크리닝-증감률] 재무상태표 기타금융부채</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6795,10 +6982,10 @@
         </is>
       </c>
       <c r="C75" s="7" t="n">
-        <v>30.58</v>
+        <v>17.96</v>
       </c>
       <c r="D75" s="7" t="n">
-        <v>30.58</v>
+        <v>17.96</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -6809,19 +6996,19 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 현금흐름표 당기손익-공정가치측정금융상품의 처분 (전기)</t>
+          <t>[스크리닝-전전기증감률] 재무상태표 기타금융부채</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>전기</t>
+          <t>전전기→전기</t>
         </is>
       </c>
       <c r="C76" s="7" t="n">
-        <v>11659750000000</v>
+        <v>23.74</v>
       </c>
       <c r="D76" s="7" t="n">
-        <v>11659750000000</v>
+        <v>23.74</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -6832,19 +7019,19 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 현금흐름표 당기손익-공정가치측정금융상품의 처분 (당기)</t>
+          <t>[스크리닝-추세이탈] 재무상태표 기타금융부채</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>추세이탈판정</t>
         </is>
       </c>
       <c r="C77" s="7" t="n">
-        <v>19103867000000</v>
+        <v>0</v>
       </c>
       <c r="D77" s="7" t="n">
-        <v>19103867000000</v>
+        <v>0</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -6855,19 +7042,19 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>[스크리닝-증감률] 현금흐름표 당기손익-공정가치측정금융상품의 처분</t>
+          <t>[스크리닝-원본금액] 재무상태표 차입부채 (전전기)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>전기→당기</t>
+          <t>전전기</t>
         </is>
       </c>
       <c r="C78" s="7" t="n">
-        <v>63.84</v>
+        <v>30986746000000</v>
       </c>
       <c r="D78" s="7" t="n">
-        <v>63.84</v>
+        <v>30986746000000</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -6878,7 +7065,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 재무상태표 발행사채 (전기)</t>
+          <t>[스크리닝-원본금액] 재무상태표 차입부채 (전기)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6887,10 +7074,10 @@
         </is>
       </c>
       <c r="C79" s="7" t="n">
-        <v>48207103000000</v>
+        <v>30117031000000</v>
       </c>
       <c r="D79" s="7" t="n">
-        <v>48207103000000</v>
+        <v>30117031000000</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -6901,7 +7088,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 재무상태표 발행사채 (당기)</t>
+          <t>[스크리닝-원본금액] 재무상태표 차입부채 (당기)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6910,10 +7097,10 @@
         </is>
       </c>
       <c r="C80" s="7" t="n">
-        <v>55583392000000</v>
+        <v>34183267000000</v>
       </c>
       <c r="D80" s="7" t="n">
-        <v>55583392000000</v>
+        <v>34183267000000</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -6924,7 +7111,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>[스크리닝-증감률] 재무상태표 발행사채</t>
+          <t>[스크리닝-증감률] 재무상태표 차입부채</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6933,10 +7120,10 @@
         </is>
       </c>
       <c r="C81" s="7" t="n">
-        <v>15.3</v>
+        <v>13.5</v>
       </c>
       <c r="D81" s="7" t="n">
-        <v>15.3</v>
+        <v>13.5</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -6947,19 +7134,19 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 현금흐름표 재무활동으로 인한 현금흐름 (전기)</t>
+          <t>[스크리닝-전전기증감률] 재무상태표 차입부채</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>전기</t>
+          <t>전전기→전기</t>
         </is>
       </c>
       <c r="C82" s="7" t="n">
-        <v>1245341000000</v>
+        <v>-2.81</v>
       </c>
       <c r="D82" s="7" t="n">
-        <v>1245341000000</v>
+        <v>-2.81</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -6970,19 +7157,19 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 현금흐름표 재무활동으로 인한 현금흐름 (당기)</t>
+          <t>[스크리닝-추세이탈] 재무상태표 차입부채</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>추세이탈판정</t>
         </is>
       </c>
       <c r="C83" s="7" t="n">
-        <v>7685336000000</v>
+        <v>0</v>
       </c>
       <c r="D83" s="7" t="n">
-        <v>7685336000000</v>
+        <v>0</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -6993,19 +7180,19 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>[스크리닝-증감률] 현금흐름표 재무활동으로 인한 현금흐름</t>
+          <t>[스크리닝-원본금액] 재무상태표 당기손익-공정가치측정금융부채 (전전기)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>전기→당기</t>
+          <t>전전기</t>
         </is>
       </c>
       <c r="C84" s="7" t="n">
-        <v>517.13</v>
+        <v>6138313000000</v>
       </c>
       <c r="D84" s="7" t="n">
-        <v>517.13</v>
+        <v>6138313000000</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -7016,7 +7203,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 재무상태표 기타금융부채 (전기)</t>
+          <t>[스크리닝-원본금액] 재무상태표 당기손익-공정가치측정금융부채 (전기)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7025,10 +7212,10 @@
         </is>
       </c>
       <c r="C85" s="7" t="n">
-        <v>32314051000000</v>
+        <v>9896597000000</v>
       </c>
       <c r="D85" s="7" t="n">
-        <v>32314051000000</v>
+        <v>9896597000000</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -7039,7 +7226,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 재무상태표 기타금융부채 (당기)</t>
+          <t>[스크리닝-원본금액] 재무상태표 당기손익-공정가치측정금융부채 (당기)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7048,10 +7235,10 @@
         </is>
       </c>
       <c r="C86" s="7" t="n">
-        <v>38118058000000</v>
+        <v>6356934000000</v>
       </c>
       <c r="D86" s="7" t="n">
-        <v>38118058000000</v>
+        <v>6356934000000</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -7062,7 +7249,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>[스크리닝-증감률] 재무상태표 기타금융부채</t>
+          <t>[스크리닝-증감률] 재무상태표 당기손익-공정가치측정금융부채</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7071,10 +7258,10 @@
         </is>
       </c>
       <c r="C87" s="7" t="n">
-        <v>17.96</v>
+        <v>-35.77</v>
       </c>
       <c r="D87" s="7" t="n">
-        <v>17.96</v>
+        <v>-35.77</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -7085,19 +7272,19 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 재무상태표 차입부채 (전기)</t>
+          <t>[스크리닝-전전기증감률] 재무상태표 당기손익-공정가치측정금융부채</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>전기</t>
+          <t>전전기→전기</t>
         </is>
       </c>
       <c r="C88" s="7" t="n">
-        <v>30117031000000</v>
+        <v>61.23</v>
       </c>
       <c r="D88" s="7" t="n">
-        <v>30117031000000</v>
+        <v>61.23</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -7108,19 +7295,19 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 재무상태표 차입부채 (당기)</t>
+          <t>[스크리닝-추세이탈] 재무상태표 당기손익-공정가치측정금융부채</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>추세이탈판정</t>
         </is>
       </c>
       <c r="C89" s="7" t="n">
-        <v>34183267000000</v>
+        <v>1</v>
       </c>
       <c r="D89" s="7" t="n">
-        <v>34183267000000</v>
+        <v>1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -7131,19 +7318,19 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>[스크리닝-증감률] 재무상태표 차입부채</t>
+          <t>[스크리닝-원본금액] 포괄손익계산서 상각후원가측정금융부채 이자비용 (전전기)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>전기→당기</t>
+          <t>전전기</t>
         </is>
       </c>
       <c r="C90" s="7" t="n">
-        <v>13.5</v>
+        <v>11899014000000</v>
       </c>
       <c r="D90" s="7" t="n">
-        <v>13.5</v>
+        <v>11899014000000</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -7154,7 +7341,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 현금흐름표 발행사채의 상환 (전기)</t>
+          <t>[스크리닝-원본금액] 포괄손익계산서 상각후원가측정금융부채 이자비용 (전기)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7163,10 +7350,10 @@
         </is>
       </c>
       <c r="C91" s="7" t="n">
-        <v>35473345000000</v>
+        <v>13127005000000</v>
       </c>
       <c r="D91" s="7" t="n">
-        <v>35473345000000</v>
+        <v>13127005000000</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -7177,7 +7364,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 현금흐름표 발행사채의 상환 (당기)</t>
+          <t>[스크리닝-원본금액] 포괄손익계산서 상각후원가측정금융부채 이자비용 (당기)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7186,10 +7373,10 @@
         </is>
       </c>
       <c r="C92" s="7" t="n">
-        <v>31611225000000</v>
+        <v>11401953000000</v>
       </c>
       <c r="D92" s="7" t="n">
-        <v>31611225000000</v>
+        <v>11401953000000</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -7200,7 +7387,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>[스크리닝-증감률] 현금흐름표 발행사채의 상환</t>
+          <t>[스크리닝-증감률] 포괄손익계산서 상각후원가측정금융부채 이자비용</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7209,10 +7396,10 @@
         </is>
       </c>
       <c r="C93" s="7" t="n">
-        <v>-10.89</v>
+        <v>-13.14</v>
       </c>
       <c r="D93" s="7" t="n">
-        <v>-10.89</v>
+        <v>-13.14</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -7223,19 +7410,19 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 재무상태표 당기손익-공정가치측정금융부채 (전기)</t>
+          <t>[스크리닝-전전기증감률] 포괄손익계산서 상각후원가측정금융부채 이자비용</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>전기</t>
+          <t>전전기→전기</t>
         </is>
       </c>
       <c r="C94" s="7" t="n">
-        <v>9896597000000</v>
+        <v>10.32</v>
       </c>
       <c r="D94" s="7" t="n">
-        <v>9896597000000</v>
+        <v>10.32</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -7246,19 +7433,19 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 재무상태표 당기손익-공정가치측정금융부채 (당기)</t>
+          <t>[스크리닝-추세이탈] 포괄손익계산서 상각후원가측정금융부채 이자비용</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>추세이탈판정</t>
         </is>
       </c>
       <c r="C95" s="7" t="n">
-        <v>6356934000000</v>
+        <v>0</v>
       </c>
       <c r="D95" s="7" t="n">
-        <v>6356934000000</v>
+        <v>0</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -7269,19 +7456,19 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>[스크리닝-증감률] 재무상태표 당기손익-공정가치측정금융부채</t>
+          <t>[스크리닝-원본금액] 현금흐름표 영업활동으로 인한 자산ㆍ부채의 변동 (전전기)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>전기→당기</t>
+          <t>전전기</t>
         </is>
       </c>
       <c r="C96" s="7" t="n">
-        <v>-35.77</v>
+        <v>-4116666000000</v>
       </c>
       <c r="D96" s="7" t="n">
-        <v>-35.77</v>
+        <v>-4116666000000</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -7292,7 +7479,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 현금흐름표 기초 현금및현금성자산 (전기)</t>
+          <t>[스크리닝-원본금액] 현금흐름표 영업활동으로 인한 자산ㆍ부채의 변동 (전기)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7301,10 +7488,10 @@
         </is>
       </c>
       <c r="C97" s="7" t="n">
-        <v>30556618000000</v>
+        <v>-13479204000000</v>
       </c>
       <c r="D97" s="7" t="n">
-        <v>30556618000000</v>
+        <v>-13479204000000</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -7315,7 +7502,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 현금흐름표 기초 현금및현금성자산 (당기)</t>
+          <t>[스크리닝-원본금액] 현금흐름표 영업활동으로 인한 자산ㆍ부채의 변동 (당기)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7324,10 +7511,10 @@
         </is>
       </c>
       <c r="C98" s="7" t="n">
-        <v>27281123000000</v>
+        <v>9225268000000</v>
       </c>
       <c r="D98" s="7" t="n">
-        <v>27281123000000</v>
+        <v>9225268000000</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -7338,7 +7525,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>[스크리닝-증감률] 현금흐름표 기초 현금및현금성자산</t>
+          <t>[스크리닝-분류:부호전환] 현금흐름표 영업활동으로 인한 자산ㆍ부채의 변동</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7347,10 +7534,10 @@
         </is>
       </c>
       <c r="C99" s="7" t="n">
-        <v>-10.72</v>
+        <v>1</v>
       </c>
       <c r="D99" s="7" t="n">
-        <v>-10.72</v>
+        <v>1</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -7361,19 +7548,19 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 현금흐름표 상각후원가측정유가증권의 상환 (전기)</t>
+          <t>[스크리닝-전전기증감률] 현금흐름표 영업활동으로 인한 자산ㆍ부채의 변동</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>전기</t>
+          <t>전전기→전기</t>
         </is>
       </c>
       <c r="C100" s="7" t="n">
-        <v>7634677000000</v>
+        <v>-227.43</v>
       </c>
       <c r="D100" s="7" t="n">
-        <v>7634677000000</v>
+        <v>-227.43</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -7384,19 +7571,19 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 현금흐름표 상각후원가측정유가증권의 상환 (당기)</t>
+          <t>[스크리닝-추세이탈] 현금흐름표 영업활동으로 인한 자산ㆍ부채의 변동</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>당기</t>
+          <t>추세이탈판정</t>
         </is>
       </c>
       <c r="C101" s="7" t="n">
-        <v>5900990000000</v>
+        <v>0</v>
       </c>
       <c r="D101" s="7" t="n">
-        <v>5900990000000</v>
+        <v>0</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -7407,19 +7594,19 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>[스크리닝-증감률] 현금흐름표 상각후원가측정유가증권의 상환</t>
+          <t>[스크리닝-원본금액] 현금흐름표 영업활동으로 인한 현금흐름 (전전기)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>전기→당기</t>
+          <t>전전기</t>
         </is>
       </c>
       <c r="C102" s="7" t="n">
-        <v>-22.71</v>
+        <v>1621942000000</v>
       </c>
       <c r="D102" s="7" t="n">
-        <v>-22.71</v>
+        <v>1621942000000</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -7430,7 +7617,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 포괄손익계산서 상각후원가측정금융부채 이자비용 (전기)</t>
+          <t>[스크리닝-원본금액] 현금흐름표 영업활동으로 인한 현금흐름 (전기)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -7439,10 +7626,10 @@
         </is>
       </c>
       <c r="C103" s="7" t="n">
-        <v>13127005000000</v>
+        <v>-6129300000000</v>
       </c>
       <c r="D103" s="7" t="n">
-        <v>13127005000000</v>
+        <v>-6129300000000</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -7453,7 +7640,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>[스크리닝-원본금액] 포괄손익계산서 상각후원가측정금융부채 이자비용 (당기)</t>
+          <t>[스크리닝-원본금액] 현금흐름표 영업활동으로 인한 현금흐름 (당기)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -7462,10 +7649,10 @@
         </is>
       </c>
       <c r="C104" s="7" t="n">
-        <v>11401953000000</v>
+        <v>13642391000000</v>
       </c>
       <c r="D104" s="7" t="n">
-        <v>11401953000000</v>
+        <v>13642391000000</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -7476,7 +7663,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>[스크리닝-증감률] 포괄손익계산서 상각후원가측정금융부채 이자비용</t>
+          <t>[스크리닝-분류:부호전환] 현금흐름표 영업활동으로 인한 현금흐름</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -7485,10 +7672,10 @@
         </is>
       </c>
       <c r="C105" s="7" t="n">
-        <v>-13.14</v>
+        <v>1</v>
       </c>
       <c r="D105" s="7" t="n">
-        <v>-13.14</v>
+        <v>1</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -7499,12 +7686,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>스크리닝 완전성(포함됐어야 할 계정 누락 없음)</t>
+          <t>[스크리닝-추세이탈] 현금흐름표 영업활동으로 인한 현금흐름</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>전기→당기</t>
+          <t>추세이탈판정</t>
         </is>
       </c>
       <c r="C106" s="7" t="n">
@@ -7522,21 +7709,1815 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
+          <t>[스크리닝-원본금액] 현금흐름표 현금및현금성자산의 증가(감소) (전전기)</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>전전기</t>
+        </is>
+      </c>
+      <c r="C107" s="7" t="n">
+        <v>-3662530000000</v>
+      </c>
+      <c r="D107" s="7" t="n">
+        <v>-3662530000000</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 현금및현금성자산의 증가(감소) (전기)</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C108" s="7" t="n">
+        <v>-3275495000000</v>
+      </c>
+      <c r="D108" s="7" t="n">
+        <v>-3275495000000</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 현금및현금성자산의 증가(감소) (당기)</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C109" s="7" t="n">
+        <v>11218556000000</v>
+      </c>
+      <c r="D109" s="7" t="n">
+        <v>11218556000000</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>[스크리닝-분류:부호전환] 현금흐름표 현금및현금성자산의 증가(감소)</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C110" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D110" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>[스크리닝-전전기증감률] 현금흐름표 현금및현금성자산의 증가(감소)</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>전전기→전기</t>
+        </is>
+      </c>
+      <c r="C111" s="7" t="n">
+        <v>10.57</v>
+      </c>
+      <c r="D111" s="7" t="n">
+        <v>10.57</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>[스크리닝-추세이탈] 현금흐름표 현금및현금성자산의 증가(감소)</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>추세이탈판정</t>
+        </is>
+      </c>
+      <c r="C112" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 상각후원가측정대출채권및기타금융자산 (전전기)</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>전전기</t>
+        </is>
+      </c>
+      <c r="C113" s="7" t="n">
+        <v>-18598117000000</v>
+      </c>
+      <c r="D113" s="7" t="n">
+        <v>-18598117000000</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 상각후원가측정대출채권및기타금융자산 (전기)</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C114" s="7" t="n">
+        <v>-21703969000000</v>
+      </c>
+      <c r="D114" s="7" t="n">
+        <v>-21703969000000</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 상각후원가측정대출채권및기타금융자산 (당기)</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C115" s="7" t="n">
+        <v>-8369230000000</v>
+      </c>
+      <c r="D115" s="7" t="n">
+        <v>-8369230000000</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 현금흐름표 상각후원가측정대출채권및기타금융자산</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C116" s="7" t="n">
+        <v>61.44</v>
+      </c>
+      <c r="D116" s="7" t="n">
+        <v>61.44</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>[스크리닝-전전기증감률] 현금흐름표 상각후원가측정대출채권및기타금융자산</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>전전기→전기</t>
+        </is>
+      </c>
+      <c r="C117" s="7" t="n">
+        <v>-16.7</v>
+      </c>
+      <c r="D117" s="7" t="n">
+        <v>-16.7</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>[스크리닝-추세이탈] 현금흐름표 상각후원가측정대출채권및기타금융자산</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>추세이탈판정</t>
+        </is>
+      </c>
+      <c r="C118" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D118" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 기타포괄손익-공정가치측정금융자산의 취득 (전전기)</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>전전기</t>
+        </is>
+      </c>
+      <c r="C119" s="7" t="n">
+        <v>24211531000000</v>
+      </c>
+      <c r="D119" s="7" t="n">
+        <v>24211531000000</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 기타포괄손익-공정가치측정금융자산의 취득 (전기)</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C120" s="7" t="n">
+        <v>31718677000000</v>
+      </c>
+      <c r="D120" s="7" t="n">
+        <v>31718677000000</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 기타포괄손익-공정가치측정금융자산의 취득 (당기)</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C121" s="7" t="n">
+        <v>43073556000000</v>
+      </c>
+      <c r="D121" s="7" t="n">
+        <v>43073556000000</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 현금흐름표 기타포괄손익-공정가치측정금융자산의 취득</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C122" s="7" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="D122" s="7" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>[스크리닝-전전기증감률] 현금흐름표 기타포괄손익-공정가치측정금융자산의 취득</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>전전기→전기</t>
+        </is>
+      </c>
+      <c r="C123" s="7" t="n">
+        <v>31.01</v>
+      </c>
+      <c r="D123" s="7" t="n">
+        <v>31.01</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>[스크리닝-추세이탈] 현금흐름표 기타포괄손익-공정가치측정금융자산의 취득</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>추세이탈판정</t>
+        </is>
+      </c>
+      <c r="C124" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D124" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 현금및현금성자산 (전전기)</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>전전기</t>
+        </is>
+      </c>
+      <c r="C125" s="7" t="n">
+        <v>30556618000000</v>
+      </c>
+      <c r="D125" s="7" t="n">
+        <v>30556618000000</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 현금및현금성자산 (전기)</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C126" s="7" t="n">
+        <v>27281123000000</v>
+      </c>
+      <c r="D126" s="7" t="n">
+        <v>27281123000000</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 현금및현금성자산 (당기)</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C127" s="7" t="n">
+        <v>38499679000000</v>
+      </c>
+      <c r="D127" s="7" t="n">
+        <v>38499679000000</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 현금흐름표 현금및현금성자산</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C128" s="7" t="n">
+        <v>41.12</v>
+      </c>
+      <c r="D128" s="7" t="n">
+        <v>41.12</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>[스크리닝-전전기증감률] 현금흐름표 현금및현금성자산</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>전전기→전기</t>
+        </is>
+      </c>
+      <c r="C129" s="7" t="n">
+        <v>-10.72</v>
+      </c>
+      <c r="D129" s="7" t="n">
+        <v>-10.72</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>[스크리닝-추세이탈] 현금흐름표 현금및현금성자산</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>추세이탈판정</t>
+        </is>
+      </c>
+      <c r="C130" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D130" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 예수부채 (전전기)</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>전전기</t>
+        </is>
+      </c>
+      <c r="C131" s="7" t="n">
+        <v>15176465000000</v>
+      </c>
+      <c r="D131" s="7" t="n">
+        <v>15176465000000</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 예수부채 (전기)</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C132" s="7" t="n">
+        <v>3411535000000</v>
+      </c>
+      <c r="D132" s="7" t="n">
+        <v>3411535000000</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 예수부채 (당기)</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C133" s="7" t="n">
+        <v>13839807000000</v>
+      </c>
+      <c r="D133" s="7" t="n">
+        <v>13839807000000</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 현금흐름표 예수부채</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C134" s="7" t="n">
+        <v>305.68</v>
+      </c>
+      <c r="D134" s="7" t="n">
+        <v>305.68</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>[스크리닝-전전기증감률] 현금흐름표 예수부채</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>전전기→전기</t>
+        </is>
+      </c>
+      <c r="C135" s="7" t="n">
+        <v>-77.52</v>
+      </c>
+      <c r="D135" s="7" t="n">
+        <v>-77.52</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>[스크리닝-추세이탈] 현금흐름표 예수부채</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>추세이탈판정</t>
+        </is>
+      </c>
+      <c r="C136" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D136" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 투자활동으로 인한 현금흐름 (전전기)</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>전전기</t>
+        </is>
+      </c>
+      <c r="C137" s="7" t="n">
+        <v>-2254141000000</v>
+      </c>
+      <c r="D137" s="7" t="n">
+        <v>-2254141000000</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 투자활동으로 인한 현금흐름 (전기)</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C138" s="7" t="n">
+        <v>-34299000000</v>
+      </c>
+      <c r="D138" s="7" t="n">
+        <v>-34299000000</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 투자활동으로 인한 현금흐름 (당기)</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C139" s="7" t="n">
+        <v>-9880603000000</v>
+      </c>
+      <c r="D139" s="7" t="n">
+        <v>-9880603000000</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 현금흐름표 투자활동으로 인한 현금흐름</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C140" s="7" t="n">
+        <v>-28707.26</v>
+      </c>
+      <c r="D140" s="7" t="n">
+        <v>-28707.26</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>[스크리닝-전전기증감률] 현금흐름표 투자활동으로 인한 현금흐름</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>전전기→전기</t>
+        </is>
+      </c>
+      <c r="C141" s="7" t="n">
+        <v>98.48</v>
+      </c>
+      <c r="D141" s="7" t="n">
+        <v>98.48</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>[스크리닝-추세이탈] 현금흐름표 투자활동으로 인한 현금흐름</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>추세이탈판정</t>
+        </is>
+      </c>
+      <c r="C142" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D142" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 당기손익-공정가치측정금융상품의 취득 (전전기)</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>전전기</t>
+        </is>
+      </c>
+      <c r="C143" s="7" t="n">
+        <v>12167823000000</v>
+      </c>
+      <c r="D143" s="7" t="n">
+        <v>12167823000000</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 당기손익-공정가치측정금융상품의 취득 (전기)</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C144" s="7" t="n">
+        <v>11111809000000</v>
+      </c>
+      <c r="D144" s="7" t="n">
+        <v>11111809000000</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 당기손익-공정가치측정금융상품의 취득 (당기)</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C145" s="7" t="n">
+        <v>20087654000000</v>
+      </c>
+      <c r="D145" s="7" t="n">
+        <v>20087654000000</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 현금흐름표 당기손익-공정가치측정금융상품의 취득</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C146" s="7" t="n">
+        <v>80.78</v>
+      </c>
+      <c r="D146" s="7" t="n">
+        <v>80.78</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>[스크리닝-전전기증감률] 현금흐름표 당기손익-공정가치측정금융상품의 취득</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>전전기→전기</t>
+        </is>
+      </c>
+      <c r="C147" s="7" t="n">
+        <v>-8.68</v>
+      </c>
+      <c r="D147" s="7" t="n">
+        <v>-8.68</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>[스크리닝-추세이탈] 현금흐름표 당기손익-공정가치측정금융상품의 취득</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>추세이탈판정</t>
+        </is>
+      </c>
+      <c r="C148" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D148" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 기타포괄손익-공정가치측정금융자산의 처분 (전전기)</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>전전기</t>
+        </is>
+      </c>
+      <c r="C149" s="7" t="n">
+        <v>20648897000000</v>
+      </c>
+      <c r="D149" s="7" t="n">
+        <v>20648897000000</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 기타포괄손익-공정가치측정금융자산의 처분 (전기)</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C150" s="7" t="n">
+        <v>26921313000000</v>
+      </c>
+      <c r="D150" s="7" t="n">
+        <v>26921313000000</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 기타포괄손익-공정가치측정금융자산의 처분 (당기)</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C151" s="7" t="n">
+        <v>35153473000000</v>
+      </c>
+      <c r="D151" s="7" t="n">
+        <v>35153473000000</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 현금흐름표 기타포괄손익-공정가치측정금융자산의 처분</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C152" s="7" t="n">
+        <v>30.58</v>
+      </c>
+      <c r="D152" s="7" t="n">
+        <v>30.58</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>[스크리닝-전전기증감률] 현금흐름표 기타포괄손익-공정가치측정금융자산의 처분</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>전전기→전기</t>
+        </is>
+      </c>
+      <c r="C153" s="7" t="n">
+        <v>30.38</v>
+      </c>
+      <c r="D153" s="7" t="n">
+        <v>30.38</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>[스크리닝-추세이탈] 현금흐름표 기타포괄손익-공정가치측정금융자산의 처분</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>추세이탈판정</t>
+        </is>
+      </c>
+      <c r="C154" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D154" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 당기손익-공정가치측정금융상품의 처분 (전전기)</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>전전기</t>
+        </is>
+      </c>
+      <c r="C155" s="7" t="n">
+        <v>10487513000000</v>
+      </c>
+      <c r="D155" s="7" t="n">
+        <v>10487513000000</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 당기손익-공정가치측정금융상품의 처분 (전기)</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C156" s="7" t="n">
+        <v>11659750000000</v>
+      </c>
+      <c r="D156" s="7" t="n">
+        <v>11659750000000</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 당기손익-공정가치측정금융상품의 처분 (당기)</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C157" s="7" t="n">
+        <v>19103867000000</v>
+      </c>
+      <c r="D157" s="7" t="n">
+        <v>19103867000000</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 현금흐름표 당기손익-공정가치측정금융상품의 처분</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C158" s="7" t="n">
+        <v>63.84</v>
+      </c>
+      <c r="D158" s="7" t="n">
+        <v>63.84</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>[스크리닝-전전기증감률] 현금흐름표 당기손익-공정가치측정금융상품의 처분</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>전전기→전기</t>
+        </is>
+      </c>
+      <c r="C159" s="7" t="n">
+        <v>11.18</v>
+      </c>
+      <c r="D159" s="7" t="n">
+        <v>11.18</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>[스크리닝-추세이탈] 현금흐름표 당기손익-공정가치측정금융상품의 처분</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>추세이탈판정</t>
+        </is>
+      </c>
+      <c r="C160" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D160" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 재무활동으로 인한 현금흐름 (전전기)</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>전전기</t>
+        </is>
+      </c>
+      <c r="C161" s="7" t="n">
+        <v>-2860177000000</v>
+      </c>
+      <c r="D161" s="7" t="n">
+        <v>-2860177000000</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 재무활동으로 인한 현금흐름 (전기)</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C162" s="7" t="n">
+        <v>1245341000000</v>
+      </c>
+      <c r="D162" s="7" t="n">
+        <v>1245341000000</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 재무활동으로 인한 현금흐름 (당기)</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C163" s="7" t="n">
+        <v>7685336000000</v>
+      </c>
+      <c r="D163" s="7" t="n">
+        <v>7685336000000</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 현금흐름표 재무활동으로 인한 현금흐름</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C164" s="7" t="n">
+        <v>517.13</v>
+      </c>
+      <c r="D164" s="7" t="n">
+        <v>517.13</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>[스크리닝-추세이탈] 현금흐름표 재무활동으로 인한 현금흐름</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>추세이탈판정</t>
+        </is>
+      </c>
+      <c r="C165" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D165" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 발행사채의 상환 (전전기)</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>전전기</t>
+        </is>
+      </c>
+      <c r="C166" s="7" t="n">
+        <v>34329491000000</v>
+      </c>
+      <c r="D166" s="7" t="n">
+        <v>34329491000000</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 발행사채의 상환 (전기)</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C167" s="7" t="n">
+        <v>35473345000000</v>
+      </c>
+      <c r="D167" s="7" t="n">
+        <v>35473345000000</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 발행사채의 상환 (당기)</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C168" s="7" t="n">
+        <v>31611225000000</v>
+      </c>
+      <c r="D168" s="7" t="n">
+        <v>31611225000000</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 현금흐름표 발행사채의 상환</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C169" s="7" t="n">
+        <v>-10.89</v>
+      </c>
+      <c r="D169" s="7" t="n">
+        <v>-10.89</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>[스크리닝-전전기증감률] 현금흐름표 발행사채의 상환</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>전전기→전기</t>
+        </is>
+      </c>
+      <c r="C170" s="7" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="D170" s="7" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>[스크리닝-추세이탈] 현금흐름표 발행사채의 상환</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>추세이탈판정</t>
+        </is>
+      </c>
+      <c r="C171" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D171" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 기초 현금및현금성자산 (전전기)</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>전전기</t>
+        </is>
+      </c>
+      <c r="C172" s="7" t="n">
+        <v>34219148000000</v>
+      </c>
+      <c r="D172" s="7" t="n">
+        <v>34219148000000</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 기초 현금및현금성자산 (전기)</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C173" s="7" t="n">
+        <v>30556618000000</v>
+      </c>
+      <c r="D173" s="7" t="n">
+        <v>30556618000000</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 기초 현금및현금성자산 (당기)</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C174" s="7" t="n">
+        <v>27281123000000</v>
+      </c>
+      <c r="D174" s="7" t="n">
+        <v>27281123000000</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 현금흐름표 기초 현금및현금성자산</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C175" s="7" t="n">
+        <v>-10.72</v>
+      </c>
+      <c r="D175" s="7" t="n">
+        <v>-10.72</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>[스크리닝-전전기증감률] 현금흐름표 기초 현금및현금성자산</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>전전기→전기</t>
+        </is>
+      </c>
+      <c r="C176" s="7" t="n">
+        <v>-10.7</v>
+      </c>
+      <c r="D176" s="7" t="n">
+        <v>-10.7</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>[스크리닝-추세이탈] 현금흐름표 기초 현금및현금성자산</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>추세이탈판정</t>
+        </is>
+      </c>
+      <c r="C177" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D177" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 상각후원가측정유가증권의 상환 (전전기)</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>전전기</t>
+        </is>
+      </c>
+      <c r="C178" s="7" t="n">
+        <v>8727124000000</v>
+      </c>
+      <c r="D178" s="7" t="n">
+        <v>8727124000000</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 상각후원가측정유가증권의 상환 (전기)</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>전기</t>
+        </is>
+      </c>
+      <c r="C179" s="7" t="n">
+        <v>7634677000000</v>
+      </c>
+      <c r="D179" s="7" t="n">
+        <v>7634677000000</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>[스크리닝-원본금액] 현금흐름표 상각후원가측정유가증권의 상환 (당기)</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>당기</t>
+        </is>
+      </c>
+      <c r="C180" s="7" t="n">
+        <v>5900990000000</v>
+      </c>
+      <c r="D180" s="7" t="n">
+        <v>5900990000000</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>[스크리닝-증감률] 현금흐름표 상각후원가측정유가증권의 상환</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C181" s="7" t="n">
+        <v>-22.71</v>
+      </c>
+      <c r="D181" s="7" t="n">
+        <v>-22.71</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>[스크리닝-전전기증감률] 현금흐름표 상각후원가측정유가증권의 상환</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>전전기→전기</t>
+        </is>
+      </c>
+      <c r="C182" s="7" t="n">
+        <v>-12.52</v>
+      </c>
+      <c r="D182" s="7" t="n">
+        <v>-12.52</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>[스크리닝-추세이탈] 현금흐름표 상각후원가측정유가증권의 상환</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>추세이탈판정</t>
+        </is>
+      </c>
+      <c r="C183" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D183" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>스크리닝 완전성(포함됐어야 할 계정 누락 없음)</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>전기→당기</t>
+        </is>
+      </c>
+      <c r="C184" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D184" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
           <t>스크리닝 정확성(기준 미달 오탐 없음)</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
+      <c r="B185" t="inlineStr">
         <is>
           <t>전기→당기</t>
         </is>
       </c>
-      <c r="C107" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D107" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E107" t="inlineStr">
+      <c r="C185" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D185" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E185" t="inlineStr">
         <is>
           <t>일치</t>
         </is>
